--- a/thesis/additional_tables.xlsx
+++ b/thesis/additional_tables.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\00_PhD\01_poglavja\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93046A82-2CE4-4CA7-9858-F7F8EBBB038F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0624B00-5694-4867-9612-5E320692FD14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{DB19BBB1-5072-4616-B9F3-8CA8F5F54A58}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{DB19BBB1-5072-4616-B9F3-8CA8F5F54A58}"/>
   </bookViews>
   <sheets>
-    <sheet name="additional_table1" sheetId="3" r:id="rId1"/>
-    <sheet name="genes_sporulation" sheetId="2" r:id="rId2"/>
+    <sheet name="participants_info" sheetId="4" r:id="rId1"/>
+    <sheet name="sequencing_table" sheetId="3" r:id="rId2"/>
+    <sheet name="genes_sporulation" sheetId="2" r:id="rId3"/>
+    <sheet name="etoh_h_comparison" sheetId="5" r:id="rId4"/>
+    <sheet name="CFU_C_saudiense" sheetId="6" r:id="rId5"/>
+    <sheet name="MALDI_C_saudisense" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="391">
   <si>
     <t>abrB</t>
   </si>
@@ -720,60 +724,15 @@
     <t>Comparison of isolation protocols</t>
   </si>
   <si>
-    <t>Optimization of protocol for spore DNA isolation from human stool samples</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitudinal study </t>
-  </si>
-  <si>
     <t xml:space="preserve">Sequencing platform </t>
   </si>
   <si>
-    <t>MiSeq</t>
-  </si>
-  <si>
-    <t>NextSeq</t>
-  </si>
-  <si>
     <t xml:space="preserve">Type of sequencing </t>
   </si>
   <si>
-    <t>Amplicon (V3-V4 region of the 16S rRNA gene)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polymerase </t>
-  </si>
-  <si>
-    <t>KAPA HiFI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q5 </t>
-  </si>
-  <si>
     <t>Q5</t>
   </si>
   <si>
-    <t xml:space="preserve">Total number of reads </t>
-  </si>
-  <si>
-    <t> 3 258 569</t>
-  </si>
-  <si>
-    <t> 4 000 965</t>
-  </si>
-  <si>
-    <t>62 793 747</t>
-  </si>
-  <si>
-    <t>0.001% of all reads</t>
-  </si>
-  <si>
-    <t>0,0001% of all reads</t>
-  </si>
-  <si>
-    <t>Average number of reads per sample</t>
-  </si>
-  <si>
     <t> 90515.8</t>
   </si>
   <si>
@@ -783,33 +742,6 @@
     <t>270662.7</t>
   </si>
   <si>
-    <t xml:space="preserve">Min / Max number of reads in a sample </t>
-  </si>
-  <si>
-    <t> 12542 / 153 530</t>
-  </si>
-  <si>
-    <t> 3 / 85784</t>
-  </si>
-  <si>
-    <t>61388 / 884743</t>
-  </si>
-  <si>
-    <t>Number of reads per sample (rarefaction depth)</t>
-  </si>
-  <si>
-    <t> 50 000</t>
-  </si>
-  <si>
-    <t> 10 000</t>
-  </si>
-  <si>
-    <t>150 000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRA project number </t>
-  </si>
-  <si>
     <t>PRJNA887005</t>
   </si>
   <si>
@@ -819,77 +751,480 @@
     <t>PRJNA1124620 </t>
   </si>
   <si>
-    <t>DNBSeq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shotgun metagenomic sequencing bulk microbiota samples </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shotgun metagenomic sequencing of ethanol treated samples </t>
-  </si>
-  <si>
     <t>Phi29</t>
   </si>
   <si>
-    <t>116/116</t>
-  </si>
-  <si>
-    <t>116/85</t>
-  </si>
-  <si>
-    <t>4e7 / 5e7</t>
-  </si>
-  <si>
-    <t>5e6 / 1e8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clean 1: Percentage of reads remaining after qualitiy filtering (mean/min/max) </t>
-  </si>
-  <si>
-    <t>98,5 / 88,8 / 99,3</t>
-  </si>
-  <si>
-    <t>51,2 / 22,9 / 98,3</t>
-  </si>
-  <si>
-    <t>Clean 2: Percentage of reads remaining after removal of human sequences (mean/min/max)</t>
-  </si>
-  <si>
-    <t>50,5 / 22,3 / 98,3</t>
-  </si>
-  <si>
-    <t>Sucessfully sequenced</t>
-  </si>
-  <si>
-    <t>5 700 000 000</t>
-  </si>
-  <si>
-    <t>4 600 000 000</t>
-  </si>
-  <si>
-    <t>49 000 000</t>
-  </si>
-  <si>
-    <t>55 000 000</t>
-  </si>
-  <si>
-    <t>OTUs with less than reads removed</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>234/6 removed including both negative controls</t>
-  </si>
-  <si>
-    <t>Longitudinal study</t>
+    <t xml:space="preserve">Participant </t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age </t>
+  </si>
+  <si>
+    <t>regular</t>
+  </si>
+  <si>
+    <t>omega3, vitaminD, complex B. Q10, probiotics</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Living environment </t>
+  </si>
+  <si>
+    <t>urban/flat</t>
+  </si>
+  <si>
+    <t>urban/house</t>
+  </si>
+  <si>
+    <t>urban/NA</t>
+  </si>
+  <si>
+    <t>Diet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">omnivore </t>
+  </si>
+  <si>
+    <t xml:space="preserve">lactose-free omnivore </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regular supplements </t>
+  </si>
+  <si>
+    <t xml:space="preserve">omega3 </t>
+  </si>
+  <si>
+    <t>protein powder</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digestion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Phylum                </t>
+  </si>
+  <si>
+    <t>Bacillota</t>
+  </si>
+  <si>
+    <t>0.453</t>
+  </si>
+  <si>
+    <t>Bacteroidota</t>
+  </si>
+  <si>
+    <t>0.341</t>
+  </si>
+  <si>
+    <t>Actinomycetota</t>
+  </si>
+  <si>
+    <t>0.0362</t>
+  </si>
+  <si>
+    <t>Pseudomonadota</t>
+  </si>
+  <si>
+    <t>0.0822</t>
+  </si>
+  <si>
+    <t>Verrucomicrobiota</t>
+  </si>
+  <si>
+    <t>0.0456</t>
+  </si>
+  <si>
+    <t>unclassified Bacteria</t>
+  </si>
+  <si>
+    <t>0.0284</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>0.0140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relative abundance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stool </t>
+  </si>
+  <si>
+    <t>Heat shock 30 min</t>
+  </si>
+  <si>
+    <t>0.935</t>
+  </si>
+  <si>
+    <t>0.00335</t>
+  </si>
+  <si>
+    <t>0.0436</t>
+  </si>
+  <si>
+    <t>0.0089</t>
+  </si>
+  <si>
+    <t>0.00476</t>
+  </si>
+  <si>
+    <t>0.00443</t>
+  </si>
+  <si>
+    <t>0.0004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946    </t>
+  </si>
+  <si>
+    <t>0.00269</t>
+  </si>
+  <si>
+    <t>0.0307</t>
+  </si>
+  <si>
+    <t>0.0122</t>
+  </si>
+  <si>
+    <t>0.00446</t>
+  </si>
+  <si>
+    <t>0.00357</t>
+  </si>
+  <si>
+    <t>0.0000593</t>
+  </si>
+  <si>
+    <t>Heat shock 60 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.943</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0000536</t>
+  </si>
+  <si>
+    <t>0.0439</t>
+  </si>
+  <si>
+    <t>0.0109</t>
+  </si>
+  <si>
+    <t>0.000404</t>
+  </si>
+  <si>
+    <t>0.00219</t>
+  </si>
+  <si>
+    <t>0.0000107</t>
+  </si>
+  <si>
+    <t>0.902</t>
+  </si>
+  <si>
+    <t>0.0000182</t>
+  </si>
+  <si>
+    <t>0.0731</t>
+  </si>
+  <si>
+    <t>0.0048</t>
+  </si>
+  <si>
+    <t>0.0000909</t>
+  </si>
+  <si>
+    <t>0.0198</t>
+  </si>
+  <si>
+    <t>EtOH 70%</t>
+  </si>
+  <si>
+    <t>EtOH 100%</t>
+  </si>
+  <si>
+    <t>NR</t>
+  </si>
+  <si>
+    <t>H005</t>
+  </si>
+  <si>
+    <t>H007</t>
+  </si>
+  <si>
+    <t>H009</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>ml</t>
+  </si>
+  <si>
+    <t>CFU/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFU/ml </t>
+  </si>
+  <si>
+    <t>Plating volume</t>
+  </si>
+  <si>
+    <t>Original sample</t>
+  </si>
+  <si>
+    <t>Score [log]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isolate number </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detected species </t>
+  </si>
+  <si>
+    <t>Clostridium saudiense</t>
+  </si>
+  <si>
+    <t>Clostridium paraputrificum</t>
+  </si>
+  <si>
+    <t>Intestinibacter bartletti</t>
+  </si>
+  <si>
+    <t>No organism identification possible</t>
+  </si>
+  <si>
+    <t>No growth after picking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H009 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">All samples </t>
+  </si>
+  <si>
+    <t>Sequenced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illumina </t>
+  </si>
+  <si>
+    <t>Illumina + Nanopore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detected species (MALDI) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detected species (pubMLST) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clostridium saudiense + Clostridium paraputrificium </t>
+  </si>
+  <si>
+    <t>ni rasti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ni rasti </t>
+  </si>
+  <si>
+    <t>Frezzer</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Illumina MiSeq</t>
+  </si>
+  <si>
+    <t>BGI DNBSeq</t>
+  </si>
+  <si>
+    <t>44/45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of samples/ sucessfully seqenced </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read length </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean number of reads per sample </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtering parameters </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project accession </t>
+  </si>
+  <si>
+    <t>Oxford Nanopore MinION</t>
+  </si>
+  <si>
+    <t>Illumina NextSeq2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longitudinal study of gut microbiota and ethanol-treated stool samples </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shotgun metagenomic sequencing </t>
+  </si>
+  <si>
+    <t>Comaprison of isolate genomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole genome sequencing </t>
+  </si>
+  <si>
+    <t>Polymerase</t>
+  </si>
+  <si>
+    <t>Kapa HiFi</t>
+  </si>
+  <si>
+    <t>36/36</t>
+  </si>
+  <si>
+    <t>Comparison of ethanol and heat shock in elimination of vegetative cells from stool samples and subsequent cultivation of sporeformers</t>
+  </si>
+  <si>
+    <t>Optimization of pre-treatment for DNA isolation from spore-forming bacteria in stool samples</t>
+  </si>
+  <si>
+    <t>28/28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative control </t>
+  </si>
+  <si>
+    <t>Not sequenced due to low DNA concetration</t>
+  </si>
+  <si>
+    <t>34/34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not included in experiment, control for experiment was untreated stool sample </t>
+  </si>
+  <si>
+    <t>Not sequenced due to low DNA concentration, controls were untreated stool sample and stool sample treated with ethanol and heat shock, but not EMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not sequenced, as it was sequenced with amplicon sequencing </t>
+  </si>
+  <si>
+    <t>Amplicon sequencing (V3-V4 region of the 16S rRNA gene)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indexing </t>
+  </si>
+  <si>
+    <t>Rapid Barcoding Kit 96 SQK-RBK110.96</t>
+  </si>
+  <si>
+    <t>NEBNext Ultra II FS DNA Library Prep Kit for Illumina</t>
+  </si>
+  <si>
+    <t>16S Metagenomic Sequencing Library Preparation protocol</t>
+  </si>
+  <si>
+    <t>MGI Sequencing Prep Kit</t>
+  </si>
+  <si>
+    <t>Ligation</t>
+  </si>
+  <si>
+    <t>236/230</t>
+  </si>
+  <si>
+    <t>201/234</t>
+  </si>
+  <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <t>Paired-end 300 bp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paired-end 150 bp </t>
+  </si>
+  <si>
+    <t xml:space="preserve">N50 1.22 kbp </t>
+  </si>
+  <si>
+    <t>50 000 000</t>
+  </si>
+  <si>
+    <t>Q &gt; 10, read length &gt; 1000 bp</t>
+  </si>
+  <si>
+    <t>98,5% /50,5% (microbiota / sporobiota)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MiSeq SOP mothur, with rarefaction to: </t>
+  </si>
+  <si>
+    <t>50 000, remove OTUs &lt; 10 reads</t>
+  </si>
+  <si>
+    <t>10 000, remove OTUs &lt; 10 reads</t>
+  </si>
+  <si>
+    <t>150 000, remove OTUs &lt; 62 reads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experiment </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average % reads removed after filtering per sample </t>
+  </si>
+  <si>
+    <t>Trimmomatic ILLUMINACLIP:NEBPE-PE.fa:2:30:10, LEADING:10, TRAILING:10, SLIDINGWINDOW:4:20, MINLEN:40</t>
+  </si>
+  <si>
+    <t>&lt; 10% uncertain bases, Q &gt; 20, more than 90% identity to host (GRCh38)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="165" formatCode="0.E+00"/>
+  </numFmts>
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -925,13 +1260,61 @@
       <family val="1"/>
       <charset val="238"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC5C8C6"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF949494"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFBCBCBC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -943,24 +1326,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -972,22 +1347,18 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1003,32 +1374,130 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1413,271 +1882,610 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAE398DA-232C-4FEE-A95F-A67F85B82E84}">
-  <dimension ref="A1:J20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCDCE0B0-CF68-43D8-A24E-A8B21C4C0ADF}">
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="19.42578125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" style="6" customWidth="1"/>
-    <col min="6" max="10" width="19.42578125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="6" max="6" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="9"/>
-      <c r="B1" s="10" t="s">
+    <row r="1" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B2" s="10">
+        <v>34</v>
+      </c>
+      <c r="C2" s="11">
+        <v>22.605591909577633</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" s="10">
+        <v>25</v>
+      </c>
+      <c r="C3" s="11">
+        <v>22.204081632653061</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="10">
+        <v>27</v>
+      </c>
+      <c r="C4" s="11">
+        <v>23.848030481620569</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" s="10">
+        <v>37</v>
+      </c>
+      <c r="C5" s="11">
+        <v>23.510204081632654</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" s="10">
+        <v>28</v>
+      </c>
+      <c r="C6" s="11">
+        <v>23.12406058503873</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" s="10">
+        <v>27</v>
+      </c>
+      <c r="C7" s="11">
+        <v>32.508521651306651</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="B8" s="10">
+        <v>27</v>
+      </c>
+      <c r="C8" s="11">
+        <v>26.038781163434905</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" s="10">
+        <v>43</v>
+      </c>
+      <c r="C9" s="11">
+        <v>28.727377190462509</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="12">
+        <v>30</v>
+      </c>
+      <c r="C10" s="13">
+        <v>18.078512396694215</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>248</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAE398DA-232C-4FEE-A95F-A67F85B82E84}">
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.5703125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="30.42578125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="25.42578125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="40" style="6" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="22.42578125" style="6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>341</v>
+      </c>
+      <c r="C1" s="55"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56" t="s">
+        <v>350</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>342</v>
+      </c>
+      <c r="G1" s="56" t="s">
+        <v>350</v>
+      </c>
+      <c r="H1" s="56" t="s">
+        <v>349</v>
+      </c>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+    </row>
+    <row r="2" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="D1" s="10" t="s">
+      <c r="C2" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="D2" s="62" t="s">
+        <v>359</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>351</v>
+      </c>
+      <c r="F2" s="59"/>
+      <c r="G2" s="55" t="s">
+        <v>353</v>
+      </c>
+      <c r="H2" s="55"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="G1" s="12"/>
-      <c r="J1" s="7"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="B3" s="59" t="s">
+        <v>367</v>
+      </c>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="56" t="s">
+        <v>352</v>
+      </c>
+      <c r="G3" s="56" t="s">
+        <v>354</v>
+      </c>
+      <c r="H3" s="56"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+    </row>
+    <row r="4" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>371</v>
+      </c>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="56" t="s">
+        <v>372</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="H4" s="56" t="s">
+        <v>369</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="C5" s="59" t="s">
         <v>229</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="56" t="s">
+        <v>236</v>
+      </c>
+      <c r="G5" s="56" t="s">
+        <v>229</v>
+      </c>
+      <c r="H5" s="56" t="s">
+        <v>373</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+    </row>
+    <row r="6" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>357</v>
+      </c>
+      <c r="C6" s="56" t="s">
+        <v>363</v>
+      </c>
+      <c r="D6" s="56" t="s">
+        <v>360</v>
+      </c>
+      <c r="E6" s="56" t="s">
+        <v>374</v>
+      </c>
+      <c r="F6" s="56" t="s">
+        <v>375</v>
+      </c>
+      <c r="G6" s="56" t="s">
+        <v>343</v>
+      </c>
+      <c r="H6" s="57"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+    </row>
+    <row r="7" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="E7" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="F7" s="56" t="s">
+        <v>366</v>
+      </c>
+      <c r="G7" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="H7" s="56" t="s">
+        <v>376</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="B8" s="55" t="s">
+        <v>377</v>
+      </c>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55" t="s">
+        <v>378</v>
+      </c>
+      <c r="G8" s="55"/>
+      <c r="H8" s="56" t="s">
+        <v>379</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+    </row>
+    <row r="9" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="D2" s="10" t="s">
+      <c r="C9" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="G2" s="13"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" spans="1:10" ht="39" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="D9" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="E9" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="F9" s="60" t="s">
+        <v>380</v>
+      </c>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+    </row>
+    <row r="10" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="59" t="s">
+        <v>347</v>
+      </c>
+      <c r="B10" s="61" t="s">
+        <v>383</v>
+      </c>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="59" t="s">
+        <v>390</v>
+      </c>
+      <c r="G10" s="59" t="s">
+        <v>389</v>
+      </c>
+      <c r="H10" s="55" t="s">
+        <v>381</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+    </row>
+    <row r="11" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="59"/>
+      <c r="B11" s="56" t="s">
+        <v>384</v>
+      </c>
+      <c r="C11" s="56" t="s">
+        <v>385</v>
+      </c>
+      <c r="D11" s="56" t="s">
+        <v>385</v>
+      </c>
+      <c r="E11" s="56" t="s">
+        <v>386</v>
+      </c>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+    </row>
+    <row r="12" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="B12" s="56"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56" t="s">
+        <v>382</v>
+      </c>
+      <c r="G12" s="58">
+        <v>0.95</v>
+      </c>
+      <c r="H12" s="57"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+    </row>
+    <row r="13" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="J3" s="7"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="C13" s="59" t="s">
         <v>234</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="D13" s="59"/>
+      <c r="E13" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="15" t="s">
-        <v>263</v>
-      </c>
-      <c r="G4" s="15"/>
-      <c r="J4" s="7"/>
-    </row>
-    <row r="5" spans="1:10" ht="39" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="J5" s="7"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="J6" s="7"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>277</v>
-      </c>
-      <c r="J7" s="7"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="J8" s="7"/>
-    </row>
-    <row r="9" spans="1:10" ht="39" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="J9" s="7"/>
-    </row>
-    <row r="10" spans="1:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>270</v>
-      </c>
-      <c r="J10" s="7"/>
-    </row>
-    <row r="11" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="20" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="8"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F1:G1"/>
+  <mergeCells count="14">
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F811F764-2817-42B1-BB85-AB1C44C4F3B3}">
   <dimension ref="A1:V65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3444,4 +4252,3609 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA0C9990-F6EB-4079-9807-3DC74FA9CD4F}">
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="26"/>
+      <c r="B1" s="48" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>287</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>302</v>
+      </c>
+      <c r="F9" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="H11" s="21"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="22"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="22"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F15" s="18"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F16" s="18"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+    </row>
+    <row r="17" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="F17" s="18"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+    </row>
+    <row r="18" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="F18" s="18"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+    </row>
+    <row r="19" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="F19" s="18"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+    </row>
+    <row r="20" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="F20" s="18"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+    </row>
+    <row r="21" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="F21" s="18"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+    </row>
+    <row r="22" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+    </row>
+    <row r="23" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+    </row>
+    <row r="24" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+    </row>
+    <row r="25" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9DE55F8-E723-4EB4-9908-92E8B4327F36}">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F1">
+        <v>0.1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="30">
+        <v>0.01</v>
+      </c>
+      <c r="B3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>320</v>
+      </c>
+      <c r="C4" s="31">
+        <v>150</v>
+      </c>
+      <c r="D4" s="31">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>106</v>
+      </c>
+      <c r="C5" s="31">
+        <v>61</v>
+      </c>
+      <c r="D5" s="31">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="B6" s="31">
+        <v>49</v>
+      </c>
+      <c r="C6" s="31">
+        <v>6</v>
+      </c>
+      <c r="D6" s="31">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>317</v>
+      </c>
+      <c r="B7" s="31">
+        <f>(B4/(A4*F1)+B5/(A5*F1)+B6/(A6*F1))/3</f>
+        <v>20933333.333333332</v>
+      </c>
+      <c r="C7" s="31">
+        <f>(C4/(A4*F1)+C5/(A5*F1)+C6/(A6*F1))/3</f>
+        <v>4533333.333333333</v>
+      </c>
+      <c r="D7" s="31">
+        <f>(D4/(A4*F1)+D5/(A5*F1)+D6/(A6*F1))/3</f>
+        <v>8606666.666666666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>318</v>
+      </c>
+      <c r="B8" s="32">
+        <v>20933333.333333332</v>
+      </c>
+      <c r="C8" s="32">
+        <v>4533333.333333333</v>
+      </c>
+      <c r="D8" s="32">
+        <v>8606666.666666666</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12C9C68-1E13-46D6-A886-AFAC0C6F13C8}">
+  <dimension ref="A1:M1048576"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.28515625" style="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="43" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" style="43" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.42578125" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>322</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>334</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>321</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>339</v>
+      </c>
+      <c r="F1" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>335</v>
+      </c>
+      <c r="I1" s="38" t="s">
+        <v>323</v>
+      </c>
+      <c r="J1" s="38" t="s">
+        <v>330</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>313</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="50" t="s">
+        <v>312</v>
+      </c>
+      <c r="B2" s="33">
+        <v>69</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D2" s="34">
+        <v>1.98</v>
+      </c>
+      <c r="E2" s="34"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="I2" s="46" t="s">
+        <v>325</v>
+      </c>
+      <c r="J2" s="6">
+        <f>COUNTIF($C$2:$C$191,I2)</f>
+        <v>24</v>
+      </c>
+      <c r="K2" s="6">
+        <f>COUNTIF($C$2:$C$58,I2)</f>
+        <v>23</v>
+      </c>
+      <c r="L2" s="6">
+        <f>COUNTIF($C$59:$C$128,I2)</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="6">
+        <f>COUNTIF($C$129:$C$191,I2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="50"/>
+      <c r="B3" s="33">
+        <v>70</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="D3" s="34">
+        <v>1.82</v>
+      </c>
+      <c r="E3" s="34"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="46" t="s">
+        <v>326</v>
+      </c>
+      <c r="J3" s="6">
+        <f>COUNTIF($C$2:$C$191,I3)</f>
+        <v>11</v>
+      </c>
+      <c r="K3" s="6">
+        <f t="shared" ref="K3:K5" si="0">COUNTIF($C$2:$C$58,I3)</f>
+        <v>4</v>
+      </c>
+      <c r="L3" s="6">
+        <f t="shared" ref="L3:L5" si="1">COUNTIF($C$59:$C$128,I3)</f>
+        <v>2</v>
+      </c>
+      <c r="M3" s="6">
+        <f t="shared" ref="M3:M5" si="2">COUNTIF($C$129:$C$191,I3)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="50"/>
+      <c r="B4" s="33">
+        <v>71</v>
+      </c>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="J4" s="6">
+        <f>COUNTIF($C$2:$C$191,I4)</f>
+        <v>87</v>
+      </c>
+      <c r="K4" s="6">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="L4" s="6">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="M4" s="6">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="50"/>
+      <c r="B5" s="33">
+        <v>72</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D5" s="34">
+        <v>1.37</v>
+      </c>
+      <c r="E5" s="34"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="33" t="s">
+        <v>327</v>
+      </c>
+      <c r="J5" s="6">
+        <f>COUNTIF($C$2:$C$191,I5)</f>
+        <v>20</v>
+      </c>
+      <c r="K5" s="6">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="L5" s="6">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="M5" s="6">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="50"/>
+      <c r="B6" s="33">
+        <v>73</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D6" s="34">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>333</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="H6" s="35"/>
+      <c r="I6" s="42" t="s">
+        <v>328</v>
+      </c>
+      <c r="J6" s="47">
+        <f t="shared" ref="J6" si="3">COUNTIF($C$2:$C$191,I6)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="47">
+        <f>COUNTIF($C$2:$C$58,"")</f>
+        <v>4</v>
+      </c>
+      <c r="L6" s="47">
+        <f>COUNTIF($C$59:$C$128,"")</f>
+        <v>19</v>
+      </c>
+      <c r="M6" s="47">
+        <f>COUNTIF($C$129:$C$191,"")</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="50"/>
+      <c r="B7" s="33">
+        <v>74</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D7" s="34">
+        <v>2.14</v>
+      </c>
+      <c r="E7" s="34"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="50"/>
+      <c r="B8" s="33">
+        <v>75</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D8" s="34">
+        <v>1.99</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G8" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="50"/>
+      <c r="B9" s="33">
+        <v>76</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D9" s="34">
+        <v>1.9</v>
+      </c>
+      <c r="E9" s="34"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35">
+        <f>COUNTIF(G:G,G6)</f>
+        <v>45</v>
+      </c>
+      <c r="J9" s="35"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="50"/>
+      <c r="B10" s="33">
+        <v>77</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D10" s="34">
+        <v>2</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G10" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="50"/>
+      <c r="B11" s="33">
+        <v>78</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D11" s="34">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="E11" s="34"/>
+      <c r="F11" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G11" s="44"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="50"/>
+      <c r="B12" s="33">
+        <v>79</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D12" s="34">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="E12" s="34"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="50"/>
+      <c r="B13" s="33">
+        <v>80</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D13" s="34">
+        <v>1.85</v>
+      </c>
+      <c r="E13" s="34"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="50"/>
+      <c r="B14" s="33">
+        <v>81</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D14" s="34">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="E14" s="34"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="50"/>
+      <c r="B15" s="33">
+        <v>82</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D15" s="34">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="E15" s="34"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="50"/>
+      <c r="B16" s="33">
+        <v>83</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="D16" s="34">
+        <v>1.94</v>
+      </c>
+      <c r="E16" s="34"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="50"/>
+      <c r="B17" s="33">
+        <v>84</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D17" s="34">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="E17" s="34"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="50"/>
+      <c r="B18" s="33">
+        <v>85</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D18" s="34">
+        <v>1.45</v>
+      </c>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="50"/>
+      <c r="B19" s="33">
+        <v>86</v>
+      </c>
+      <c r="C19" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D19" s="34">
+        <v>1.79</v>
+      </c>
+      <c r="E19" s="34"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="50"/>
+      <c r="B20" s="33">
+        <v>87</v>
+      </c>
+      <c r="C20" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D20" s="34">
+        <v>1.85</v>
+      </c>
+      <c r="E20" s="34"/>
+      <c r="F20" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G20" s="44"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="50"/>
+      <c r="B21" s="33">
+        <v>88</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D21" s="34">
+        <v>1.32</v>
+      </c>
+      <c r="E21" s="34"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="50"/>
+      <c r="B22" s="33">
+        <v>89</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D22" s="34">
+        <v>2.21</v>
+      </c>
+      <c r="E22" s="34"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="50"/>
+      <c r="B23" s="33">
+        <v>90</v>
+      </c>
+      <c r="C23" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D23" s="34">
+        <v>1.99</v>
+      </c>
+      <c r="E23" s="34"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="50"/>
+      <c r="B24" s="33">
+        <v>91</v>
+      </c>
+      <c r="C24" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D24" s="34">
+        <v>1.97</v>
+      </c>
+      <c r="E24" s="34"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="50"/>
+      <c r="B25" s="33">
+        <v>92</v>
+      </c>
+      <c r="C25" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D25" s="34">
+        <v>1.39</v>
+      </c>
+      <c r="E25" s="34"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="50"/>
+      <c r="B26" s="33">
+        <v>93</v>
+      </c>
+      <c r="C26" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D26" s="34">
+        <v>2.14</v>
+      </c>
+      <c r="E26" s="34"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="50"/>
+      <c r="B27" s="33">
+        <v>94</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D27" s="34">
+        <v>1.99</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F27" s="35" t="s">
+        <v>333</v>
+      </c>
+      <c r="G27" s="44" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="50"/>
+      <c r="B28" s="33">
+        <v>95</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D28" s="34">
+        <v>1.95</v>
+      </c>
+      <c r="E28" s="34"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="50"/>
+      <c r="B29" s="33">
+        <v>96</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D29" s="34">
+        <v>2.02</v>
+      </c>
+      <c r="E29" s="34"/>
+      <c r="F29" s="35" t="s">
+        <v>338</v>
+      </c>
+      <c r="G29" s="44"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="50"/>
+      <c r="B30" s="33">
+        <v>97</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D30" s="34">
+        <v>1.92</v>
+      </c>
+      <c r="E30" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F30" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G30" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="50"/>
+      <c r="B31" s="33">
+        <v>98</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D31" s="34">
+        <v>2.08</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F31" s="35" t="s">
+        <v>333</v>
+      </c>
+      <c r="G31" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="50"/>
+      <c r="B32" s="33">
+        <v>99</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D32" s="34">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="E32" s="34"/>
+      <c r="F32" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G32" s="44"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="50"/>
+      <c r="B33" s="33">
+        <v>100</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="D33" s="34">
+        <v>1.72</v>
+      </c>
+      <c r="E33" s="34"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="35"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="50"/>
+      <c r="B34" s="33">
+        <v>101</v>
+      </c>
+      <c r="C34" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D34" s="34">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="E34" s="34"/>
+      <c r="F34" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G34" s="44"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="50"/>
+      <c r="B35" s="33">
+        <v>102</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D35" s="34">
+        <v>2</v>
+      </c>
+      <c r="E35" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F35" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G35" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="50"/>
+      <c r="B36" s="33">
+        <v>103</v>
+      </c>
+      <c r="C36" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D36" s="34">
+        <v>1.84</v>
+      </c>
+      <c r="E36" s="34"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="50"/>
+      <c r="B37" s="33">
+        <v>104</v>
+      </c>
+      <c r="C37" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D37" s="34">
+        <v>2.08</v>
+      </c>
+      <c r="E37" s="34"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="35"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="50"/>
+      <c r="B38" s="33">
+        <v>105</v>
+      </c>
+      <c r="D38" s="34"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="35"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="50"/>
+      <c r="B39" s="33">
+        <v>106</v>
+      </c>
+      <c r="C39" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D39" s="34">
+        <v>1.32</v>
+      </c>
+      <c r="E39" s="34"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="35"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="50"/>
+      <c r="B40" s="33">
+        <v>107</v>
+      </c>
+      <c r="C40" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D40" s="34">
+        <v>2.06</v>
+      </c>
+      <c r="E40" s="34"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="35"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="50"/>
+      <c r="B41" s="33">
+        <v>108</v>
+      </c>
+      <c r="C41" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D41" s="34">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="E41" s="34"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="35"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="50"/>
+      <c r="B42" s="33">
+        <v>109</v>
+      </c>
+      <c r="C42" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D42" s="34">
+        <v>2.11</v>
+      </c>
+      <c r="E42" s="34"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="50"/>
+      <c r="B43" s="33">
+        <v>110</v>
+      </c>
+      <c r="C43" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D43" s="34">
+        <v>2.06</v>
+      </c>
+      <c r="E43" s="34"/>
+      <c r="F43" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G43" s="44"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="50"/>
+      <c r="B44" s="33">
+        <v>111</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D44" s="34">
+        <v>1.54</v>
+      </c>
+      <c r="E44" s="34"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="35"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="50"/>
+      <c r="B45" s="33">
+        <v>112</v>
+      </c>
+      <c r="C45" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D45" s="34">
+        <v>2.14</v>
+      </c>
+      <c r="E45" s="34"/>
+      <c r="F45" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G45" s="44"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="50"/>
+      <c r="B46" s="33">
+        <v>113</v>
+      </c>
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="35"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="50"/>
+      <c r="B47" s="33">
+        <v>114</v>
+      </c>
+      <c r="C47" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D47" s="34">
+        <v>1.57</v>
+      </c>
+      <c r="E47" s="34"/>
+      <c r="F47" s="35"/>
+      <c r="G47" s="35"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="50"/>
+      <c r="B48" s="33">
+        <v>115</v>
+      </c>
+      <c r="C48" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D48" s="34">
+        <v>1.97</v>
+      </c>
+      <c r="E48" s="34"/>
+      <c r="F48" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G48" s="44"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="50"/>
+      <c r="B49" s="33">
+        <v>116</v>
+      </c>
+      <c r="C49" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D49" s="34">
+        <v>1.95</v>
+      </c>
+      <c r="E49" s="34"/>
+      <c r="F49" s="35"/>
+      <c r="G49" s="35"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="50"/>
+      <c r="B50" s="33">
+        <v>117</v>
+      </c>
+      <c r="D50" s="34"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="35"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="50"/>
+      <c r="B51" s="33">
+        <v>118</v>
+      </c>
+      <c r="C51" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D51" s="34">
+        <v>1.85</v>
+      </c>
+      <c r="E51" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F51" s="35" t="s">
+        <v>333</v>
+      </c>
+      <c r="G51" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="50"/>
+      <c r="B52" s="33">
+        <v>119</v>
+      </c>
+      <c r="C52" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="D52" s="34">
+        <v>1.76</v>
+      </c>
+      <c r="E52" s="34"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="50"/>
+      <c r="B53" s="33">
+        <v>120</v>
+      </c>
+      <c r="C53" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D53" s="34">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="E53" s="34"/>
+      <c r="F53" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G53" s="44"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="50"/>
+      <c r="B54" s="33">
+        <v>121</v>
+      </c>
+      <c r="C54" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D54" s="34">
+        <v>1.84</v>
+      </c>
+      <c r="E54" s="34"/>
+      <c r="F54" s="35"/>
+      <c r="G54" s="35"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="50"/>
+      <c r="B55" s="33">
+        <v>123</v>
+      </c>
+      <c r="C55" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D55" s="34">
+        <v>1.95</v>
+      </c>
+      <c r="E55" s="34"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="50"/>
+      <c r="B56" s="33">
+        <v>124</v>
+      </c>
+      <c r="C56" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D56" s="34">
+        <v>1.92</v>
+      </c>
+      <c r="E56" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F56" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G56" s="44" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="50"/>
+      <c r="B57" s="33">
+        <v>125</v>
+      </c>
+      <c r="C57" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D57" s="34">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="E57" s="34"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="51"/>
+      <c r="B58" s="42">
+        <v>126</v>
+      </c>
+      <c r="C58" s="45" t="s">
+        <v>324</v>
+      </c>
+      <c r="D58" s="41">
+        <v>2.08</v>
+      </c>
+      <c r="E58" s="41" t="s">
+        <v>340</v>
+      </c>
+      <c r="F58" s="52" t="s">
+        <v>332</v>
+      </c>
+      <c r="G58" s="45" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="B59" s="33">
+        <v>127</v>
+      </c>
+      <c r="C59" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D59" s="34">
+        <v>1.71</v>
+      </c>
+      <c r="E59" s="34"/>
+      <c r="F59" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G59" s="44"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="50"/>
+      <c r="B60" s="33">
+        <v>128</v>
+      </c>
+      <c r="C60" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D60" s="34">
+        <v>1.99</v>
+      </c>
+      <c r="E60" s="34"/>
+      <c r="F60" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G60" s="44"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="50"/>
+      <c r="B61" s="33">
+        <v>129</v>
+      </c>
+      <c r="C61" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D61" s="34">
+        <v>1.96</v>
+      </c>
+      <c r="E61" s="34"/>
+      <c r="F61" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G61" s="44"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="50"/>
+      <c r="B62" s="33">
+        <v>130</v>
+      </c>
+      <c r="C62" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D62" s="34">
+        <v>2.04</v>
+      </c>
+      <c r="E62" s="34"/>
+      <c r="F62" s="34" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="50"/>
+      <c r="B63" s="33">
+        <v>131</v>
+      </c>
+      <c r="C63" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D63" s="34">
+        <v>1.3</v>
+      </c>
+      <c r="E63" s="34"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="50"/>
+      <c r="B64" s="33">
+        <v>132</v>
+      </c>
+      <c r="C64" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D64" s="34">
+        <v>1.47</v>
+      </c>
+      <c r="E64" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F64" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G64" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="50"/>
+      <c r="B65" s="33">
+        <v>133</v>
+      </c>
+      <c r="C65" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="D65" s="34">
+        <v>1.96</v>
+      </c>
+      <c r="E65" s="34"/>
+      <c r="F65" s="35"/>
+      <c r="G65" s="35"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="50"/>
+      <c r="B66" s="33">
+        <v>134</v>
+      </c>
+      <c r="D66" s="34"/>
+      <c r="E66" s="34"/>
+      <c r="F66" s="35"/>
+      <c r="G66" s="35"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="50"/>
+      <c r="B67" s="33">
+        <v>135</v>
+      </c>
+      <c r="C67" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D67" s="34">
+        <v>2.23</v>
+      </c>
+      <c r="E67" s="34"/>
+      <c r="F67" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G67" s="44"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="50"/>
+      <c r="B68" s="33">
+        <v>136</v>
+      </c>
+      <c r="D68" s="34"/>
+      <c r="E68" s="34"/>
+      <c r="F68" s="35"/>
+      <c r="G68" s="35"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="50"/>
+      <c r="B69" s="33">
+        <v>137</v>
+      </c>
+      <c r="C69" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D69" s="34">
+        <v>2.09</v>
+      </c>
+      <c r="E69" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F69" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G69" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="50"/>
+      <c r="B70" s="33">
+        <v>138</v>
+      </c>
+      <c r="C70" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D70" s="34">
+        <v>1.3</v>
+      </c>
+      <c r="E70" s="34"/>
+      <c r="F70" s="35"/>
+      <c r="G70" s="35"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="50"/>
+      <c r="B71" s="33">
+        <v>139</v>
+      </c>
+      <c r="C71" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D71" s="34">
+        <v>2.09</v>
+      </c>
+      <c r="E71" s="34"/>
+      <c r="F71" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G71" s="44"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="50"/>
+      <c r="B72" s="33">
+        <v>140</v>
+      </c>
+      <c r="D72" s="34"/>
+      <c r="E72" s="34"/>
+      <c r="F72" s="35"/>
+      <c r="G72" s="35"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="50"/>
+      <c r="B73" s="33">
+        <v>141</v>
+      </c>
+      <c r="D73" s="34"/>
+      <c r="E73" s="34"/>
+      <c r="F73" s="35"/>
+      <c r="G73" s="35"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="50"/>
+      <c r="B74" s="33">
+        <v>142</v>
+      </c>
+      <c r="D74" s="34"/>
+      <c r="E74" s="34"/>
+      <c r="F74" s="35"/>
+      <c r="G74" s="35"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="50"/>
+      <c r="B75" s="33">
+        <v>143</v>
+      </c>
+      <c r="C75" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="D75" s="34">
+        <v>1.84</v>
+      </c>
+      <c r="E75" s="34"/>
+      <c r="F75" s="35"/>
+      <c r="G75" s="35"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="50"/>
+      <c r="B76" s="33">
+        <v>144</v>
+      </c>
+      <c r="D76" s="34"/>
+      <c r="E76" s="34"/>
+      <c r="F76" s="35"/>
+      <c r="G76" s="35"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="50"/>
+      <c r="B77" s="33">
+        <v>145</v>
+      </c>
+      <c r="C77" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D77" s="34">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="E77" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F77" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G77" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="50"/>
+      <c r="B78" s="33">
+        <v>146</v>
+      </c>
+      <c r="C78" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D78" s="34">
+        <v>2.09</v>
+      </c>
+      <c r="E78" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F78" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G78" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="50"/>
+      <c r="B79" s="33">
+        <v>147</v>
+      </c>
+      <c r="D79" s="34"/>
+      <c r="E79" s="34"/>
+      <c r="F79" s="35"/>
+      <c r="G79" s="35"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="50"/>
+      <c r="B80" s="33">
+        <v>148</v>
+      </c>
+      <c r="C80" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D80" s="34">
+        <v>2.11</v>
+      </c>
+      <c r="E80" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F80" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G80" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="50"/>
+      <c r="B81" s="33">
+        <v>149</v>
+      </c>
+      <c r="C81" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D81" s="34">
+        <v>1.93</v>
+      </c>
+      <c r="E81" s="34"/>
+      <c r="F81" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G81" s="44"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="50"/>
+      <c r="B82" s="33">
+        <v>150</v>
+      </c>
+      <c r="D82" s="34"/>
+      <c r="E82" s="34"/>
+      <c r="F82" s="35"/>
+      <c r="G82" s="35"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="50"/>
+      <c r="B83" s="33">
+        <v>151</v>
+      </c>
+      <c r="C83" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D83" s="34">
+        <v>1.96</v>
+      </c>
+      <c r="E83" s="34"/>
+      <c r="F83" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="G83" s="44"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="50"/>
+      <c r="B84" s="33">
+        <v>152</v>
+      </c>
+      <c r="C84" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D84" s="34">
+        <v>1.98</v>
+      </c>
+      <c r="E84" s="34"/>
+      <c r="F84" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="G84" s="44"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="50"/>
+      <c r="B85" s="33">
+        <v>153</v>
+      </c>
+      <c r="C85" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D85" s="34">
+        <v>1.98</v>
+      </c>
+      <c r="E85" s="34"/>
+      <c r="F85" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="G85" s="44"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="50"/>
+      <c r="B86" s="33">
+        <v>154</v>
+      </c>
+      <c r="C86" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D86" s="34">
+        <v>2.06</v>
+      </c>
+      <c r="E86" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F86" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G86" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="50"/>
+      <c r="B87" s="33">
+        <v>155</v>
+      </c>
+      <c r="C87" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D87" s="34">
+        <v>1.76</v>
+      </c>
+      <c r="E87" s="34"/>
+      <c r="F87" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="G87" s="44"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="50"/>
+      <c r="B88" s="33">
+        <v>156</v>
+      </c>
+      <c r="C88" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D88" s="34">
+        <v>2</v>
+      </c>
+      <c r="E88" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F88" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G88" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="50"/>
+      <c r="B89" s="33">
+        <v>157</v>
+      </c>
+      <c r="C89" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D89" s="34">
+        <v>1.72</v>
+      </c>
+      <c r="E89" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F89" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G89" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="50"/>
+      <c r="B90" s="33">
+        <v>158</v>
+      </c>
+      <c r="C90" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D90" s="34">
+        <v>2.15</v>
+      </c>
+      <c r="E90" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F90" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G90" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="50"/>
+      <c r="B91" s="33">
+        <v>159</v>
+      </c>
+      <c r="C91" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D91" s="34">
+        <v>1.3</v>
+      </c>
+      <c r="E91" s="34"/>
+      <c r="F91" s="35"/>
+      <c r="G91" s="35"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="50"/>
+      <c r="B92" s="33">
+        <v>160</v>
+      </c>
+      <c r="D92" s="34"/>
+      <c r="E92" s="34"/>
+      <c r="F92" s="35"/>
+      <c r="G92" s="35"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="50"/>
+      <c r="B93" s="33">
+        <v>161</v>
+      </c>
+      <c r="C93" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D93" s="34">
+        <v>1.3</v>
+      </c>
+      <c r="E93" s="34"/>
+      <c r="F93" s="35"/>
+      <c r="G93" s="35"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="50"/>
+      <c r="B94" s="33">
+        <v>162</v>
+      </c>
+      <c r="C94" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D94" s="34">
+        <v>2.02</v>
+      </c>
+      <c r="E94" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F94" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G94" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="50"/>
+      <c r="B95" s="33">
+        <v>163</v>
+      </c>
+      <c r="C95" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D95" s="34">
+        <v>1.83</v>
+      </c>
+      <c r="E95" s="34"/>
+      <c r="F95" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G95" s="44"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="50"/>
+      <c r="B96" s="33">
+        <v>164</v>
+      </c>
+      <c r="D96" s="34"/>
+      <c r="E96" s="34"/>
+      <c r="F96" s="35"/>
+      <c r="G96" s="35"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="50"/>
+      <c r="B97" s="33">
+        <v>166</v>
+      </c>
+      <c r="D97" s="34"/>
+      <c r="E97" s="34"/>
+      <c r="F97" s="35"/>
+      <c r="G97" s="35"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="50"/>
+      <c r="B98" s="33">
+        <v>167</v>
+      </c>
+      <c r="C98" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D98" s="34">
+        <v>1.93</v>
+      </c>
+      <c r="E98" s="34"/>
+      <c r="F98" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G98" s="44"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="50"/>
+      <c r="B99" s="33">
+        <v>168</v>
+      </c>
+      <c r="C99" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D99" s="34">
+        <v>1.94</v>
+      </c>
+      <c r="E99" s="34"/>
+      <c r="F99" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G99" s="44"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="50"/>
+      <c r="B100" s="33">
+        <v>169</v>
+      </c>
+      <c r="D100" s="34"/>
+      <c r="E100" s="34"/>
+      <c r="F100" s="35"/>
+      <c r="G100" s="35"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="50"/>
+      <c r="B101" s="33">
+        <v>170</v>
+      </c>
+      <c r="C101" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D101" s="34"/>
+      <c r="E101" s="34"/>
+      <c r="F101" s="35"/>
+      <c r="G101" s="35"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="50"/>
+      <c r="B102" s="33">
+        <v>171</v>
+      </c>
+      <c r="C102" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D102" s="34">
+        <v>2.09</v>
+      </c>
+      <c r="E102" s="34"/>
+      <c r="F102" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G102" s="44"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="50"/>
+      <c r="B103" s="33">
+        <v>172</v>
+      </c>
+      <c r="C103" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D103" s="34">
+        <v>2.08</v>
+      </c>
+      <c r="E103" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F103" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G103" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="50"/>
+      <c r="B104" s="33">
+        <v>173</v>
+      </c>
+      <c r="C104" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D104" s="34">
+        <v>1.95</v>
+      </c>
+      <c r="E104" s="34"/>
+      <c r="F104" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G104" s="44"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="50"/>
+      <c r="B105" s="33">
+        <v>174</v>
+      </c>
+      <c r="C105" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D105" s="34">
+        <v>1.93</v>
+      </c>
+      <c r="E105" s="34"/>
+      <c r="F105" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G105" s="44"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="50"/>
+      <c r="B106" s="33">
+        <v>175</v>
+      </c>
+      <c r="D106" s="34"/>
+      <c r="E106" s="34"/>
+      <c r="F106" s="35"/>
+      <c r="G106" s="35"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="50"/>
+      <c r="B107" s="33">
+        <v>176</v>
+      </c>
+      <c r="C107" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D107" s="34">
+        <v>2.06</v>
+      </c>
+      <c r="E107" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F107" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G107" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="50"/>
+      <c r="B108" s="33">
+        <v>177</v>
+      </c>
+      <c r="D108" s="34"/>
+      <c r="E108" s="34"/>
+      <c r="F108" s="35"/>
+      <c r="G108" s="35"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="50"/>
+      <c r="B109" s="33">
+        <v>178</v>
+      </c>
+      <c r="C109" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D109" s="34">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="E109" s="34"/>
+      <c r="F109" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G109" s="44"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="50"/>
+      <c r="B110" s="33">
+        <v>179</v>
+      </c>
+      <c r="C110" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D110" s="34"/>
+      <c r="E110" s="34"/>
+      <c r="F110" s="35"/>
+      <c r="G110" s="35"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="50"/>
+      <c r="B111" s="33">
+        <v>180</v>
+      </c>
+      <c r="C111" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D111" s="34">
+        <v>1.81</v>
+      </c>
+      <c r="E111" s="34"/>
+      <c r="F111" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G111" s="44"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="50"/>
+      <c r="B112" s="33">
+        <v>181</v>
+      </c>
+      <c r="C112" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D112" s="34">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="E112" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F112" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G112" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="50"/>
+      <c r="B113" s="33">
+        <v>182</v>
+      </c>
+      <c r="C113" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D113" s="34">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="E113" s="34"/>
+      <c r="F113" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G113" s="44"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="50"/>
+      <c r="B114" s="33">
+        <v>183</v>
+      </c>
+      <c r="C114" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D114" s="34">
+        <v>2</v>
+      </c>
+      <c r="E114" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F114" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G114" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="50"/>
+      <c r="B115" s="33">
+        <v>184</v>
+      </c>
+      <c r="D115" s="34"/>
+      <c r="E115" s="34"/>
+      <c r="F115" s="35"/>
+      <c r="G115" s="35"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="50"/>
+      <c r="B116" s="33">
+        <v>185</v>
+      </c>
+      <c r="D116" s="34"/>
+      <c r="E116" s="34"/>
+      <c r="F116" s="35"/>
+      <c r="G116" s="35"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="50"/>
+      <c r="B117" s="33">
+        <v>186</v>
+      </c>
+      <c r="C117" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D117" s="34">
+        <v>1.86</v>
+      </c>
+      <c r="E117" s="34"/>
+      <c r="F117" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G117" s="44"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="50"/>
+      <c r="B118" s="33">
+        <v>187</v>
+      </c>
+      <c r="C118" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D118" s="34">
+        <v>2.04</v>
+      </c>
+      <c r="E118" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F118" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G118" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="50"/>
+      <c r="B119" s="33">
+        <v>188</v>
+      </c>
+      <c r="C119" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D119" s="34">
+        <v>2.21</v>
+      </c>
+      <c r="E119" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F119" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G119" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="50"/>
+      <c r="B120" s="33">
+        <v>189</v>
+      </c>
+      <c r="C120" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D120" s="34">
+        <v>1.79</v>
+      </c>
+      <c r="E120" s="34"/>
+      <c r="F120" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G120" s="44"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="50"/>
+      <c r="B121" s="33">
+        <v>190</v>
+      </c>
+      <c r="C121" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D121" s="34">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="E121" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F121" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G121" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="50"/>
+      <c r="B122" s="33">
+        <v>191</v>
+      </c>
+      <c r="D122" s="34"/>
+      <c r="E122" s="34"/>
+      <c r="F122" s="35"/>
+      <c r="G122" s="35"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="50"/>
+      <c r="B123" s="33">
+        <v>192</v>
+      </c>
+      <c r="C123" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D123" s="34">
+        <v>1.99</v>
+      </c>
+      <c r="E123" s="34"/>
+      <c r="F123" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G123" s="44"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="50"/>
+      <c r="B124" s="33">
+        <v>193</v>
+      </c>
+      <c r="D124" s="34"/>
+      <c r="E124" s="34"/>
+      <c r="F124" s="35"/>
+      <c r="G124" s="35"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="50"/>
+      <c r="B125" s="33">
+        <v>194</v>
+      </c>
+      <c r="C125" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D125" s="34">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="E125" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F125" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G125" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="50"/>
+      <c r="B126" s="33">
+        <v>195</v>
+      </c>
+      <c r="C126" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D126" s="34">
+        <v>2.15</v>
+      </c>
+      <c r="E126" s="34"/>
+      <c r="F126" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G126" s="44"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="50"/>
+      <c r="B127" s="33">
+        <v>196</v>
+      </c>
+      <c r="C127" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D127" s="34">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="E127" s="34"/>
+      <c r="F127" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G127" s="44"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="51"/>
+      <c r="B128" s="42">
+        <v>197</v>
+      </c>
+      <c r="C128" s="45"/>
+      <c r="D128" s="41"/>
+      <c r="E128" s="41"/>
+      <c r="F128" s="52"/>
+      <c r="G128" s="52"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="49" t="s">
+        <v>314</v>
+      </c>
+      <c r="B129" s="37">
+        <v>198</v>
+      </c>
+      <c r="C129" s="40" t="s">
+        <v>327</v>
+      </c>
+      <c r="D129" s="40"/>
+      <c r="E129" s="40"/>
+      <c r="F129" s="53"/>
+      <c r="G129" s="53"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="50"/>
+      <c r="B130" s="33">
+        <v>199</v>
+      </c>
+      <c r="C130" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D130" s="34">
+        <v>1.93</v>
+      </c>
+      <c r="E130" s="34"/>
+      <c r="F130" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G130" s="44"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="50"/>
+      <c r="B131" s="33">
+        <v>200</v>
+      </c>
+      <c r="C131" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="D131" s="34">
+        <v>1.72</v>
+      </c>
+      <c r="E131" s="34"/>
+      <c r="F131" s="35"/>
+      <c r="G131" s="35"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="50"/>
+      <c r="B132" s="33">
+        <v>201</v>
+      </c>
+      <c r="C132" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D132" s="34">
+        <v>1.82</v>
+      </c>
+      <c r="E132" s="34"/>
+      <c r="F132" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G132" s="44"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="50"/>
+      <c r="B133" s="33">
+        <v>202</v>
+      </c>
+      <c r="C133" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D133" s="34">
+        <v>2.1</v>
+      </c>
+      <c r="E133" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F133" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G133" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="50"/>
+      <c r="B134" s="33">
+        <v>203</v>
+      </c>
+      <c r="C134" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D134" s="34">
+        <v>1.95</v>
+      </c>
+      <c r="E134" s="34"/>
+      <c r="F134" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G134" s="44"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="50"/>
+      <c r="B135" s="33">
+        <v>204</v>
+      </c>
+      <c r="C135" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D135" s="34">
+        <v>1.42</v>
+      </c>
+      <c r="E135" s="34"/>
+      <c r="F135" s="35"/>
+      <c r="G135" s="35"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="50"/>
+      <c r="B136" s="33">
+        <v>205</v>
+      </c>
+      <c r="C136" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D136" s="34">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="E136" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F136" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G136" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="50"/>
+      <c r="B137" s="33">
+        <v>206</v>
+      </c>
+      <c r="C137" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D137" s="34">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="E137" s="34"/>
+      <c r="F137" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G137" s="44"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="50"/>
+      <c r="B138" s="33">
+        <v>207</v>
+      </c>
+      <c r="C138" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D138" s="34">
+        <v>2.04</v>
+      </c>
+      <c r="E138" s="34"/>
+      <c r="F138" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G138" s="44"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="50"/>
+      <c r="B139" s="33">
+        <v>208</v>
+      </c>
+      <c r="C139" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D139" s="34">
+        <v>1.9</v>
+      </c>
+      <c r="E139" s="34"/>
+      <c r="F139" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G139" s="44"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="50"/>
+      <c r="B140" s="33">
+        <v>209</v>
+      </c>
+      <c r="C140" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D140" s="34">
+        <v>1.98</v>
+      </c>
+      <c r="E140" s="34"/>
+      <c r="F140" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G140" s="44"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="50"/>
+      <c r="B141" s="33">
+        <v>210</v>
+      </c>
+      <c r="C141" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D141" s="34">
+        <v>1.31</v>
+      </c>
+      <c r="E141" s="34"/>
+      <c r="F141" s="35"/>
+      <c r="G141" s="35"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="50"/>
+      <c r="B142" s="33">
+        <v>211</v>
+      </c>
+      <c r="C142" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D142" s="34">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="E142" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F142" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G142" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="50"/>
+      <c r="B143" s="33">
+        <v>212</v>
+      </c>
+      <c r="D143" s="34"/>
+      <c r="E143" s="34"/>
+      <c r="F143" s="35"/>
+      <c r="G143" s="35"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="50"/>
+      <c r="B144" s="33">
+        <v>213</v>
+      </c>
+      <c r="C144" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D144" s="34">
+        <v>2.09</v>
+      </c>
+      <c r="E144" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F144" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G144" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="50"/>
+      <c r="B145" s="33">
+        <v>214</v>
+      </c>
+      <c r="C145" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D145" s="34">
+        <v>1.56</v>
+      </c>
+      <c r="E145" s="34"/>
+      <c r="F145" s="35"/>
+      <c r="G145" s="35"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="50"/>
+      <c r="B146" s="33">
+        <v>215</v>
+      </c>
+      <c r="C146" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D146" s="34">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="E146" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F146" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G146" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="50"/>
+      <c r="B147" s="33">
+        <v>216</v>
+      </c>
+      <c r="D147" s="34"/>
+      <c r="E147" s="34"/>
+      <c r="F147" s="35"/>
+      <c r="G147" s="35"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="50"/>
+      <c r="B148" s="33">
+        <v>217</v>
+      </c>
+      <c r="C148" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D148" s="34">
+        <v>2.21</v>
+      </c>
+      <c r="E148" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F148" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G148" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="50"/>
+      <c r="B149" s="33">
+        <v>218</v>
+      </c>
+      <c r="C149" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D149" s="34">
+        <v>1.9</v>
+      </c>
+      <c r="E149" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F149" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G149" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="50"/>
+      <c r="B150" s="33">
+        <v>219</v>
+      </c>
+      <c r="C150" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D150" s="34">
+        <v>1.97</v>
+      </c>
+      <c r="E150" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F150" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G150" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="50"/>
+      <c r="B151" s="33">
+        <v>220</v>
+      </c>
+      <c r="C151" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D151" s="34">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E151" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F151" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G151" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="50"/>
+      <c r="B152" s="33">
+        <v>221</v>
+      </c>
+      <c r="C152" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D152" s="34">
+        <v>1.99</v>
+      </c>
+      <c r="E152" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F152" s="35" t="s">
+        <v>333</v>
+      </c>
+      <c r="G152" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="50"/>
+      <c r="B153" s="33">
+        <v>222</v>
+      </c>
+      <c r="C153" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D153" s="34">
+        <v>1.98</v>
+      </c>
+      <c r="E153" s="34"/>
+      <c r="F153" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="G153" s="44"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="50"/>
+      <c r="B154" s="33">
+        <v>223</v>
+      </c>
+      <c r="D154" s="34"/>
+      <c r="E154" s="34"/>
+      <c r="F154" s="35"/>
+      <c r="G154" s="35"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="50"/>
+      <c r="B155" s="33">
+        <v>224</v>
+      </c>
+      <c r="D155" s="34"/>
+      <c r="E155" s="34"/>
+      <c r="F155" s="35"/>
+      <c r="G155" s="35"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="50"/>
+      <c r="B156" s="33">
+        <v>225</v>
+      </c>
+      <c r="D156" s="34"/>
+      <c r="E156" s="34"/>
+      <c r="F156" s="35"/>
+      <c r="G156" s="35"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="50"/>
+      <c r="B157" s="33">
+        <v>226</v>
+      </c>
+      <c r="C157" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D157" s="34"/>
+      <c r="E157" s="34"/>
+      <c r="F157" s="35"/>
+      <c r="G157" s="35"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="50"/>
+      <c r="B158" s="33">
+        <v>227</v>
+      </c>
+      <c r="D158" s="34"/>
+      <c r="E158" s="34"/>
+      <c r="F158" s="35"/>
+      <c r="G158" s="35"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="50"/>
+      <c r="B159" s="33">
+        <v>228</v>
+      </c>
+      <c r="C159" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D159" s="34">
+        <v>1.78</v>
+      </c>
+      <c r="E159" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F159" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G159" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="50"/>
+      <c r="B160" s="33">
+        <v>229</v>
+      </c>
+      <c r="D160" s="34"/>
+      <c r="E160" s="34"/>
+      <c r="F160" s="35"/>
+      <c r="G160" s="35"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="50"/>
+      <c r="B161" s="33">
+        <v>230</v>
+      </c>
+      <c r="C161" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D161" s="34">
+        <v>1.74</v>
+      </c>
+      <c r="E161" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F161" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G161" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="50"/>
+      <c r="B162" s="33">
+        <v>231</v>
+      </c>
+      <c r="D162" s="34"/>
+      <c r="E162" s="34"/>
+      <c r="F162" s="35"/>
+      <c r="G162" s="35"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="50"/>
+      <c r="B163" s="33">
+        <v>232</v>
+      </c>
+      <c r="D163" s="34"/>
+      <c r="E163" s="34"/>
+      <c r="F163" s="35"/>
+      <c r="G163" s="35"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" s="50"/>
+      <c r="B164" s="33">
+        <v>233</v>
+      </c>
+      <c r="D164" s="34"/>
+      <c r="E164" s="34"/>
+      <c r="F164" s="35"/>
+      <c r="G164" s="35"/>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" s="50"/>
+      <c r="B165" s="33">
+        <v>234</v>
+      </c>
+      <c r="C165" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D165" s="34">
+        <v>2.13</v>
+      </c>
+      <c r="E165" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F165" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G165" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="50"/>
+      <c r="B166" s="33">
+        <v>235</v>
+      </c>
+      <c r="C166" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D166" s="34">
+        <v>1.94</v>
+      </c>
+      <c r="E166" s="34"/>
+      <c r="F166" s="35"/>
+      <c r="G166" s="35"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" s="50"/>
+      <c r="B167" s="33">
+        <v>236</v>
+      </c>
+      <c r="C167" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D167" s="34">
+        <v>1.85</v>
+      </c>
+      <c r="E167" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F167" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G167" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="50"/>
+      <c r="B168" s="33">
+        <v>237</v>
+      </c>
+      <c r="D168" s="34"/>
+      <c r="E168" s="34"/>
+      <c r="F168" s="35"/>
+      <c r="G168" s="35"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="50"/>
+      <c r="B169" s="33">
+        <v>238</v>
+      </c>
+      <c r="D169" s="34"/>
+      <c r="E169" s="34"/>
+      <c r="F169" s="35"/>
+      <c r="G169" s="35"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="50"/>
+      <c r="B170" s="33">
+        <v>239</v>
+      </c>
+      <c r="D170" s="34"/>
+      <c r="E170" s="34"/>
+      <c r="F170" s="35"/>
+      <c r="G170" s="35"/>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="50"/>
+      <c r="B171" s="33">
+        <v>240</v>
+      </c>
+      <c r="C171" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="D171" s="34">
+        <v>1.93</v>
+      </c>
+      <c r="E171" s="34"/>
+      <c r="F171" s="35"/>
+      <c r="G171" s="35"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="50"/>
+      <c r="B172" s="33">
+        <v>241</v>
+      </c>
+      <c r="D172" s="34"/>
+      <c r="E172" s="34"/>
+      <c r="F172" s="35"/>
+      <c r="G172" s="35"/>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" s="50"/>
+      <c r="B173" s="33">
+        <v>242</v>
+      </c>
+      <c r="D173" s="34"/>
+      <c r="E173" s="34"/>
+      <c r="F173" s="35"/>
+      <c r="G173" s="35"/>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="50"/>
+      <c r="B174" s="33">
+        <v>243</v>
+      </c>
+      <c r="C174" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="D174" s="34">
+        <v>1.93</v>
+      </c>
+      <c r="E174" s="34"/>
+      <c r="F174" s="35"/>
+      <c r="G174" s="35"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="50"/>
+      <c r="B175" s="33">
+        <v>244</v>
+      </c>
+      <c r="D175" s="34"/>
+      <c r="E175" s="34"/>
+      <c r="F175" s="35"/>
+      <c r="G175" s="35"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" s="50"/>
+      <c r="B176" s="33">
+        <v>245</v>
+      </c>
+      <c r="D176" s="34"/>
+      <c r="E176" s="34"/>
+      <c r="F176" s="35"/>
+      <c r="G176" s="35"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" s="50"/>
+      <c r="B177" s="33">
+        <v>246</v>
+      </c>
+      <c r="D177" s="34"/>
+      <c r="E177" s="34"/>
+      <c r="F177" s="35"/>
+      <c r="G177" s="35"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" s="50"/>
+      <c r="B178" s="33">
+        <v>247</v>
+      </c>
+      <c r="C178" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="D178" s="34">
+        <v>1.93</v>
+      </c>
+      <c r="E178" s="34"/>
+      <c r="F178" s="35"/>
+      <c r="G178" s="35"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" s="50"/>
+      <c r="B179" s="33">
+        <v>248</v>
+      </c>
+      <c r="D179" s="34"/>
+      <c r="E179" s="34"/>
+      <c r="F179" s="35"/>
+      <c r="G179" s="35"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" s="50"/>
+      <c r="B180" s="33">
+        <v>249</v>
+      </c>
+      <c r="D180" s="34"/>
+      <c r="E180" s="34"/>
+      <c r="F180" s="35"/>
+      <c r="G180" s="35"/>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" s="50"/>
+      <c r="B181" s="33">
+        <v>250</v>
+      </c>
+      <c r="D181" s="34"/>
+      <c r="E181" s="34"/>
+      <c r="F181" s="35"/>
+      <c r="G181" s="35"/>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="50"/>
+      <c r="B182" s="33">
+        <v>251</v>
+      </c>
+      <c r="C182" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D182" s="34">
+        <v>2.12</v>
+      </c>
+      <c r="E182" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F182" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G182" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" s="50"/>
+      <c r="B183" s="33">
+        <v>252</v>
+      </c>
+      <c r="D183" s="34"/>
+      <c r="E183" s="34"/>
+      <c r="F183" s="35"/>
+      <c r="G183" s="35"/>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" s="50"/>
+      <c r="B184" s="33">
+        <v>253</v>
+      </c>
+      <c r="D184" s="34"/>
+      <c r="E184" s="34"/>
+      <c r="F184" s="35"/>
+      <c r="G184" s="35"/>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" s="50"/>
+      <c r="B185" s="33">
+        <v>254</v>
+      </c>
+      <c r="C185" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="D185" s="34">
+        <v>1.88</v>
+      </c>
+      <c r="E185" s="34"/>
+      <c r="F185" s="35"/>
+      <c r="G185" s="35"/>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="50"/>
+      <c r="B186" s="33">
+        <v>255</v>
+      </c>
+      <c r="C186" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D186" s="34">
+        <v>1.93</v>
+      </c>
+      <c r="E186" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F186" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G186" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" s="50"/>
+      <c r="B187" s="33">
+        <v>256</v>
+      </c>
+      <c r="C187" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D187" s="34">
+        <v>1.77</v>
+      </c>
+      <c r="E187" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F187" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G187" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188" s="50"/>
+      <c r="B188" s="33">
+        <v>257</v>
+      </c>
+      <c r="C188" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D188" s="34"/>
+      <c r="E188" s="34"/>
+      <c r="F188" s="35"/>
+      <c r="G188" s="35"/>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" s="50"/>
+      <c r="B189" s="33">
+        <v>258</v>
+      </c>
+      <c r="D189" s="34"/>
+      <c r="E189" s="34"/>
+      <c r="F189" s="35"/>
+      <c r="G189" s="35"/>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" s="50"/>
+      <c r="B190" s="33">
+        <v>259</v>
+      </c>
+      <c r="C190" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="D190" s="34">
+        <v>2.04</v>
+      </c>
+      <c r="E190" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F190" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="G190" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" s="51"/>
+      <c r="B191" s="42">
+        <v>260</v>
+      </c>
+      <c r="C191" s="45"/>
+      <c r="D191" s="41"/>
+      <c r="E191" s="41"/>
+      <c r="F191" s="52"/>
+      <c r="G191" s="52"/>
+    </row>
+    <row r="1048576" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1048576" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A58"/>
+    <mergeCell ref="A59:A128"/>
+    <mergeCell ref="A129:A191"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D129:E191">
+    <cfRule type="cellIs" priority="1" operator="between">
+      <formula>1.98</formula>
+      <formula>2.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/thesis/additional_tables.xlsx
+++ b/thesis/additional_tables.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\00_PhD\01_poglavja\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBE0CEB-0A71-4489-8842-7507757C2581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175F1EA1-26DE-4547-B0A2-399B40761B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{DB19BBB1-5072-4616-B9F3-8CA8F5F54A58}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{DB19BBB1-5072-4616-B9F3-8CA8F5F54A58}"/>
   </bookViews>
   <sheets>
     <sheet name="ST1_participants_info" sheetId="4" r:id="rId1"/>
     <sheet name="ST2_probiotics" sheetId="8" r:id="rId2"/>
     <sheet name="ST3_protocol_compare" sheetId="9" r:id="rId3"/>
     <sheet name="ST4_sequencing_table" sheetId="3" r:id="rId4"/>
-    <sheet name="genes_sporulation" sheetId="2" r:id="rId5"/>
-    <sheet name="etoh_h_comparison" sheetId="5" r:id="rId6"/>
-    <sheet name="CFU_C_saudiense" sheetId="6" r:id="rId7"/>
-    <sheet name="MALDI_C_saudisense" sheetId="7" r:id="rId8"/>
+    <sheet name="ST5_breseq" sheetId="10" r:id="rId5"/>
+    <sheet name="genes_sporulation" sheetId="2" r:id="rId6"/>
+    <sheet name="etoh_h_comparison" sheetId="5" r:id="rId7"/>
+    <sheet name="CFU_C_saudiense" sheetId="6" r:id="rId8"/>
+    <sheet name="MALDI_C_saudisense" sheetId="7" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="492">
   <si>
     <t>abrB</t>
   </si>
@@ -1080,9 +1081,6 @@
     <t xml:space="preserve">Shotgun metagenomic sequencing </t>
   </si>
   <si>
-    <t>Comaprison of isolate genomes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Whole genome sequencing </t>
   </si>
   <si>
@@ -1128,9 +1126,6 @@
     <t xml:space="preserve">Indexing </t>
   </si>
   <si>
-    <t>Rapid Barcoding Kit 96 SQK-RBK110.96</t>
-  </si>
-  <si>
     <t>NEBNext Ultra II FS DNA Library Prep Kit for Illumina</t>
   </si>
   <si>
@@ -1158,15 +1153,9 @@
     <t xml:space="preserve">Paired-end 150 bp </t>
   </si>
   <si>
-    <t xml:space="preserve">N50 1.22 kbp </t>
-  </si>
-  <si>
     <t>50 000 000</t>
   </si>
   <si>
-    <t>Q &gt; 10, read length &gt; 1000 bp</t>
-  </si>
-  <si>
     <t>98,5% /50,5% (microbiota / sporobiota)</t>
   </si>
   <si>
@@ -1183,9 +1172,6 @@
   </si>
   <si>
     <t xml:space="preserve">Experiment </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average % reads removed after filtering per sample </t>
   </si>
   <si>
     <t>Trimmomatic ILLUMINACLIP:NEBPE-PE.fa:2:30:10, LEADING:10, TRAILING:10, SLIDINGWINDOW:4:20, MINLEN:40</t>
@@ -1371,6 +1357,196 @@
   <si>
     <t>2,0 ml nuclease-free tubes (Starstedt, DE) with 0.1 mm (0.25g) and 0.5 mm (0.25g) silica beads (Biospec Products, US) and ATL buffer</t>
   </si>
+  <si>
+    <t>N50 6,2 kbp</t>
+  </si>
+  <si>
+    <t>Q &gt; 10, read length &gt; 3000 bp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Population comparison of </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="238"/>
+      </rPr>
+      <t>Clostridium saudiense</t>
+    </r>
+  </si>
+  <si>
+    <t>Rapid Barcoding Kit 24 SQK-RBK114.24</t>
+  </si>
+  <si>
+    <t>5/5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average % reads after filtering per sample </t>
+  </si>
+  <si>
+    <t>95%, coverage 80x to 100x</t>
+  </si>
+  <si>
+    <t>Coverage 40x to 60x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isolate </t>
+  </si>
+  <si>
+    <t>Strain Group</t>
+  </si>
+  <si>
+    <t>Total # mutations</t>
+  </si>
+  <si>
+    <t>SNPs</t>
+  </si>
+  <si>
+    <t>Small indel</t>
+  </si>
+  <si>
+    <t>Large deletion</t>
+  </si>
+  <si>
+    <t>Large indertion</t>
+  </si>
+  <si>
+    <t>Large substitution</t>
+  </si>
+  <si>
+    <t>H005_73</t>
+  </si>
+  <si>
+    <t>H005_75</t>
+  </si>
+  <si>
+    <t>H005_77</t>
+  </si>
+  <si>
+    <t>H005_97</t>
+  </si>
+  <si>
+    <t>H005_98</t>
+  </si>
+  <si>
+    <t>H005_102</t>
+  </si>
+  <si>
+    <t>H005_118</t>
+  </si>
+  <si>
+    <t>H005_126</t>
+  </si>
+  <si>
+    <t>H005_137</t>
+  </si>
+  <si>
+    <t>H007_145</t>
+  </si>
+  <si>
+    <t>H007_146</t>
+  </si>
+  <si>
+    <t>H007_148</t>
+  </si>
+  <si>
+    <t>H007_154</t>
+  </si>
+  <si>
+    <t>H007_156</t>
+  </si>
+  <si>
+    <t>H007_157</t>
+  </si>
+  <si>
+    <t>H007_158</t>
+  </si>
+  <si>
+    <t>H007_162</t>
+  </si>
+  <si>
+    <t>H007_172</t>
+  </si>
+  <si>
+    <t>H007_176</t>
+  </si>
+  <si>
+    <t>H007_181</t>
+  </si>
+  <si>
+    <t>H007_183</t>
+  </si>
+  <si>
+    <t>H007_187</t>
+  </si>
+  <si>
+    <t>H007_188</t>
+  </si>
+  <si>
+    <t>H007_190</t>
+  </si>
+  <si>
+    <t>H007_194</t>
+  </si>
+  <si>
+    <t>H009_202</t>
+  </si>
+  <si>
+    <t>H009_205</t>
+  </si>
+  <si>
+    <t>H009_211</t>
+  </si>
+  <si>
+    <t>H009_213</t>
+  </si>
+  <si>
+    <t>H009_215</t>
+  </si>
+  <si>
+    <t>H009_217</t>
+  </si>
+  <si>
+    <t>H009_218</t>
+  </si>
+  <si>
+    <t>H009_219</t>
+  </si>
+  <si>
+    <t>H009_220</t>
+  </si>
+  <si>
+    <t>H009_221</t>
+  </si>
+  <si>
+    <t>H009_228</t>
+  </si>
+  <si>
+    <t>H009_230</t>
+  </si>
+  <si>
+    <t>H009_234</t>
+  </si>
+  <si>
+    <t>H009_236</t>
+  </si>
+  <si>
+    <t>H009_251</t>
+  </si>
+  <si>
+    <t>H009_255</t>
+  </si>
+  <si>
+    <t>H009_256</t>
+  </si>
+  <si>
+    <t>H009_259</t>
+  </si>
 </sst>
 </file>
 
@@ -1380,7 +1556,7 @@
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.E+00"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1517,6 +1693,22 @@
       <family val="1"/>
       <charset val="238"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1573,7 +1765,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1591,9 +1783,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1664,42 +1853,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1795,12 +1948,58 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2187,470 +2386,470 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCDCE0B0-CF68-43D8-A24E-A8B21C4C0ADF}">
   <dimension ref="A1:V26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" customWidth="1"/>
-    <col min="10" max="10" width="24.5703125" customWidth="1"/>
-    <col min="13" max="13" width="2.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.28515625" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
-    <col min="18" max="18" width="15.42578125" customWidth="1"/>
-    <col min="19" max="19" width="12.42578125" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.6640625" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="17.109375" customWidth="1"/>
+    <col min="8" max="8" width="18.6640625" customWidth="1"/>
+    <col min="10" max="10" width="24.5546875" customWidth="1"/>
+    <col min="13" max="13" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.33203125" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
+    <col min="18" max="18" width="15.44140625" customWidth="1"/>
+    <col min="19" max="19" width="12.44140625" customWidth="1"/>
+    <col min="20" max="20" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+    <row r="1" spans="1:22" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="62" t="s">
         <v>237</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="62" t="s">
         <v>247</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="62" t="s">
         <v>248</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="62" t="s">
         <v>249</v>
       </c>
-      <c r="E1" s="75" t="s">
-        <v>407</v>
-      </c>
-      <c r="F1" s="58" t="s">
+      <c r="E1" s="62" t="s">
+        <v>402</v>
+      </c>
+      <c r="F1" s="45" t="s">
+        <v>378</v>
+      </c>
+      <c r="G1" s="63" t="s">
+        <v>379</v>
+      </c>
+      <c r="H1" s="63" t="s">
+        <v>388</v>
+      </c>
+      <c r="I1" s="63" t="s">
+        <v>389</v>
+      </c>
+      <c r="J1" s="63" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="71" t="s">
+        <v>238</v>
+      </c>
+      <c r="B2" s="71">
+        <v>34</v>
+      </c>
+      <c r="C2" s="72">
+        <v>22.605591909577633</v>
+      </c>
+      <c r="D2" s="71" t="s">
+        <v>250</v>
+      </c>
+      <c r="E2" s="71" t="s">
+        <v>252</v>
+      </c>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="73" t="s">
+        <v>390</v>
+      </c>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+    </row>
+    <row r="3" spans="1:22" ht="24" x14ac:dyDescent="0.3">
+      <c r="A3" s="64" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" s="64">
+        <v>25</v>
+      </c>
+      <c r="C3" s="65">
+        <v>22.204081632653061</v>
+      </c>
+      <c r="D3" s="64" t="s">
+        <v>250</v>
+      </c>
+      <c r="E3" s="64" t="s">
+        <v>254</v>
+      </c>
+      <c r="F3" s="64"/>
+      <c r="G3" s="66" t="s">
+        <v>380</v>
+      </c>
+      <c r="H3" s="48" t="s">
+        <v>391</v>
+      </c>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="64" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="64">
+        <v>27</v>
+      </c>
+      <c r="C4" s="65">
+        <v>23.848030481620569</v>
+      </c>
+      <c r="D4" s="64" t="s">
+        <v>250</v>
+      </c>
+      <c r="E4" s="64" t="s">
+        <v>253</v>
+      </c>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="66" t="s">
+        <v>392</v>
+      </c>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="64" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" s="64">
+        <v>37</v>
+      </c>
+      <c r="C5" s="65">
+        <v>23.510204081632654</v>
+      </c>
+      <c r="D5" s="64" t="s">
+        <v>250</v>
+      </c>
+      <c r="E5" s="64" t="s">
+        <v>381</v>
+      </c>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="48" t="s">
+        <v>393</v>
+      </c>
+      <c r="I5" s="48" t="s">
+        <v>398</v>
+      </c>
+      <c r="J5" s="75"/>
+    </row>
+    <row r="6" spans="1:22" ht="36" x14ac:dyDescent="0.3">
+      <c r="A6" s="64" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" s="64">
+        <v>28</v>
+      </c>
+      <c r="C6" s="65">
+        <v>23.12406058503873</v>
+      </c>
+      <c r="D6" s="64" t="s">
+        <v>250</v>
+      </c>
+      <c r="E6" s="64" t="s">
+        <v>254</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>382</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>384</v>
+      </c>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="64" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" s="64">
+        <v>27</v>
+      </c>
+      <c r="C7" s="65">
+        <v>32.508521651306651</v>
+      </c>
+      <c r="D7" s="64" t="s">
+        <v>250</v>
+      </c>
+      <c r="E7" s="64" t="s">
+        <v>254</v>
+      </c>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="66" t="s">
+        <v>394</v>
+      </c>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="64" t="s">
+        <v>244</v>
+      </c>
+      <c r="B8" s="64">
+        <v>27</v>
+      </c>
+      <c r="C8" s="65">
+        <v>26.038781163434905</v>
+      </c>
+      <c r="D8" s="64" t="s">
+        <v>250</v>
+      </c>
+      <c r="E8" s="64" t="s">
+        <v>253</v>
+      </c>
+      <c r="F8" s="64"/>
+      <c r="G8" s="66" t="s">
+        <v>385</v>
+      </c>
+      <c r="H8" s="66" t="s">
+        <v>395</v>
+      </c>
+      <c r="I8" s="66" t="s">
+        <v>397</v>
+      </c>
+      <c r="J8" s="66" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="24" x14ac:dyDescent="0.3">
+      <c r="A9" s="64" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" s="64">
+        <v>43</v>
+      </c>
+      <c r="C9" s="65">
+        <v>28.727377190462509</v>
+      </c>
+      <c r="D9" s="64" t="s">
+        <v>250</v>
+      </c>
+      <c r="E9" s="64" t="s">
+        <v>254</v>
+      </c>
+      <c r="F9" s="48" t="s">
         <v>383</v>
       </c>
-      <c r="G1" s="76" t="s">
-        <v>384</v>
-      </c>
-      <c r="H1" s="76" t="s">
-        <v>393</v>
-      </c>
-      <c r="I1" s="76" t="s">
-        <v>394</v>
-      </c>
-      <c r="J1" s="76" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="84" t="s">
-        <v>238</v>
-      </c>
-      <c r="B2" s="84">
-        <v>34</v>
-      </c>
-      <c r="C2" s="85">
-        <v>22.605591909577633</v>
-      </c>
-      <c r="D2" s="84" t="s">
-        <v>250</v>
-      </c>
-      <c r="E2" s="84" t="s">
-        <v>252</v>
-      </c>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="86" t="s">
-        <v>395</v>
-      </c>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-    </row>
-    <row r="3" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="77" t="s">
-        <v>239</v>
-      </c>
-      <c r="B3" s="77">
-        <v>25</v>
-      </c>
-      <c r="C3" s="78">
-        <v>22.204081632653061</v>
-      </c>
-      <c r="D3" s="77" t="s">
-        <v>250</v>
-      </c>
-      <c r="E3" s="77" t="s">
-        <v>254</v>
-      </c>
-      <c r="F3" s="77"/>
-      <c r="G3" s="79" t="s">
-        <v>385</v>
-      </c>
-      <c r="H3" s="61" t="s">
+      <c r="G9" s="66" t="s">
+        <v>386</v>
+      </c>
+      <c r="H9" s="48" t="s">
         <v>396</v>
       </c>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
-        <v>240</v>
-      </c>
-      <c r="B4" s="77">
-        <v>27</v>
-      </c>
-      <c r="C4" s="78">
-        <v>23.848030481620569</v>
-      </c>
-      <c r="D4" s="77" t="s">
-        <v>250</v>
-      </c>
-      <c r="E4" s="77" t="s">
-        <v>253</v>
-      </c>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="79" t="s">
-        <v>397</v>
-      </c>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="77" t="s">
-        <v>241</v>
-      </c>
-      <c r="B5" s="77">
-        <v>37</v>
-      </c>
-      <c r="C5" s="78">
-        <v>23.510204081632654</v>
-      </c>
-      <c r="D5" s="77" t="s">
-        <v>250</v>
-      </c>
-      <c r="E5" s="77" t="s">
-        <v>386</v>
-      </c>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="61" t="s">
-        <v>398</v>
-      </c>
-      <c r="I5" s="61" t="s">
-        <v>403</v>
-      </c>
-      <c r="J5" s="88"/>
-    </row>
-    <row r="6" spans="1:22" ht="36" x14ac:dyDescent="0.25">
-      <c r="A6" s="77" t="s">
-        <v>242</v>
-      </c>
-      <c r="B6" s="77">
-        <v>28</v>
-      </c>
-      <c r="C6" s="78">
-        <v>23.12406058503873</v>
-      </c>
-      <c r="D6" s="77" t="s">
-        <v>250</v>
-      </c>
-      <c r="E6" s="77" t="s">
-        <v>254</v>
-      </c>
-      <c r="F6" s="61" t="s">
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+    </row>
+    <row r="10" spans="1:22" ht="36" x14ac:dyDescent="0.3">
+      <c r="A10" s="67" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="67">
+        <v>30</v>
+      </c>
+      <c r="C10" s="68">
+        <v>18.078512396694215</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>251</v>
+      </c>
+      <c r="E10" s="49" t="s">
         <v>387</v>
       </c>
-      <c r="G6" s="61" t="s">
-        <v>389</v>
-      </c>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="77" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" s="77">
-        <v>27</v>
-      </c>
-      <c r="C7" s="78">
-        <v>32.508521651306651</v>
-      </c>
-      <c r="D7" s="77" t="s">
-        <v>250</v>
-      </c>
-      <c r="E7" s="77" t="s">
-        <v>254</v>
-      </c>
-      <c r="F7" s="77"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="79" t="s">
-        <v>399</v>
-      </c>
-      <c r="I7" s="88"/>
-      <c r="J7" s="88"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="77" t="s">
-        <v>244</v>
-      </c>
-      <c r="B8" s="77">
-        <v>27</v>
-      </c>
-      <c r="C8" s="78">
-        <v>26.038781163434905</v>
-      </c>
-      <c r="D8" s="77" t="s">
-        <v>250</v>
-      </c>
-      <c r="E8" s="77" t="s">
-        <v>253</v>
-      </c>
-      <c r="F8" s="77"/>
-      <c r="G8" s="79" t="s">
-        <v>390</v>
-      </c>
-      <c r="H8" s="79" t="s">
-        <v>400</v>
-      </c>
-      <c r="I8" s="79" t="s">
-        <v>402</v>
-      </c>
-      <c r="J8" s="79" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A9" s="77" t="s">
-        <v>245</v>
-      </c>
-      <c r="B9" s="77">
-        <v>43</v>
-      </c>
-      <c r="C9" s="78">
-        <v>28.727377190462509</v>
-      </c>
-      <c r="D9" s="77" t="s">
-        <v>250</v>
-      </c>
-      <c r="E9" s="77" t="s">
-        <v>254</v>
-      </c>
-      <c r="F9" s="61" t="s">
-        <v>388</v>
-      </c>
-      <c r="G9" s="79" t="s">
-        <v>391</v>
-      </c>
-      <c r="H9" s="61" t="s">
-        <v>401</v>
-      </c>
-      <c r="I9" s="88"/>
-      <c r="J9" s="88"/>
-    </row>
-    <row r="10" spans="1:22" ht="36" x14ac:dyDescent="0.25">
-      <c r="A10" s="80" t="s">
-        <v>246</v>
-      </c>
-      <c r="B10" s="80">
-        <v>30</v>
-      </c>
-      <c r="C10" s="81">
-        <v>18.078512396694215</v>
-      </c>
-      <c r="D10" s="62" t="s">
-        <v>251</v>
-      </c>
-      <c r="E10" s="62" t="s">
-        <v>392</v>
-      </c>
-      <c r="F10" s="80"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="82"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="83"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M12" s="70"/>
-      <c r="N12" s="70"/>
-      <c r="O12" s="70"/>
-      <c r="P12" s="71"/>
-      <c r="Q12" s="71"/>
-      <c r="R12" s="71"/>
-      <c r="S12" s="71"/>
-      <c r="T12" s="71"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M13" s="59"/>
-      <c r="N13" s="59"/>
-      <c r="O13" s="60"/>
-      <c r="P13" s="59"/>
-      <c r="Q13" s="59"/>
-      <c r="R13" s="61"/>
-      <c r="S13" s="72"/>
-      <c r="T13" s="72"/>
-      <c r="U13" s="30"/>
-      <c r="V13" s="30"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M14" s="59"/>
-      <c r="N14" s="59"/>
-      <c r="O14" s="60"/>
-      <c r="P14" s="59"/>
-      <c r="Q14" s="61"/>
-      <c r="R14" s="61"/>
-      <c r="S14" s="72"/>
-      <c r="T14" s="72"/>
-      <c r="U14" s="30"/>
-      <c r="V14" s="30"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M15" s="59"/>
-      <c r="N15" s="59"/>
-      <c r="O15" s="60"/>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="59"/>
-      <c r="R15" s="61"/>
-      <c r="S15" s="72"/>
-      <c r="T15" s="73"/>
-      <c r="U15" s="30"/>
-      <c r="V15" s="30"/>
-    </row>
-    <row r="16" spans="1:22" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M16" s="59"/>
-      <c r="N16" s="59"/>
-      <c r="O16" s="60"/>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="59"/>
-      <c r="R16" s="61"/>
-      <c r="S16" s="61"/>
-      <c r="T16" s="72"/>
-      <c r="U16" s="30"/>
-      <c r="V16" s="30"/>
-    </row>
-    <row r="17" spans="13:22" x14ac:dyDescent="0.25">
-      <c r="M17" s="59"/>
-      <c r="N17" s="59"/>
-      <c r="O17" s="60"/>
-      <c r="P17" s="61"/>
-      <c r="Q17" s="61"/>
-      <c r="R17" s="72"/>
-      <c r="S17" s="72"/>
-      <c r="T17" s="72"/>
-      <c r="U17" s="30"/>
-      <c r="V17" s="30"/>
-    </row>
-    <row r="18" spans="13:22" x14ac:dyDescent="0.25">
-      <c r="M18" s="59"/>
-      <c r="N18" s="59"/>
-      <c r="O18" s="60"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="59"/>
-      <c r="R18" s="61"/>
-      <c r="S18" s="72"/>
-      <c r="T18" s="72"/>
-      <c r="U18" s="30"/>
-      <c r="V18" s="30"/>
-    </row>
-    <row r="19" spans="13:22" x14ac:dyDescent="0.25">
-      <c r="M19" s="59"/>
-      <c r="N19" s="59"/>
-      <c r="O19" s="60"/>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="61"/>
-      <c r="R19" s="61"/>
-      <c r="S19" s="61"/>
-      <c r="T19" s="61"/>
-      <c r="U19" s="30"/>
-      <c r="V19" s="30"/>
-    </row>
-    <row r="20" spans="13:22" x14ac:dyDescent="0.25">
-      <c r="M20" s="59"/>
-      <c r="N20" s="59"/>
-      <c r="O20" s="60"/>
-      <c r="P20" s="61"/>
-      <c r="Q20" s="61"/>
-      <c r="R20" s="61"/>
-      <c r="S20" s="72"/>
-      <c r="T20" s="72"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-    </row>
-    <row r="21" spans="13:22" x14ac:dyDescent="0.25">
-      <c r="M21" s="59"/>
-      <c r="N21" s="59"/>
-      <c r="O21" s="60"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="59"/>
-      <c r="R21" s="61"/>
-      <c r="S21" s="61"/>
-      <c r="T21" s="72"/>
-      <c r="U21" s="30"/>
-      <c r="V21" s="30"/>
-    </row>
-    <row r="22" spans="13:22" x14ac:dyDescent="0.25">
-      <c r="M22" s="30"/>
-      <c r="N22" s="74"/>
-      <c r="O22" s="30"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-    </row>
-    <row r="23" spans="13:22" x14ac:dyDescent="0.25">
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-    </row>
-    <row r="24" spans="13:22" x14ac:dyDescent="0.25">
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
-      <c r="P24" s="30"/>
-      <c r="Q24" s="30"/>
-      <c r="R24" s="30"/>
-      <c r="S24" s="30"/>
-      <c r="T24" s="30"/>
-      <c r="U24" s="30"/>
-      <c r="V24" s="30"/>
-    </row>
-    <row r="25" spans="13:22" x14ac:dyDescent="0.25">
-      <c r="M25" s="30"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="30"/>
-      <c r="P25" s="30"/>
-      <c r="Q25" s="30"/>
-      <c r="R25" s="30"/>
-      <c r="S25" s="30"/>
-      <c r="T25" s="30"/>
-      <c r="U25" s="30"/>
-      <c r="V25" s="30"/>
-    </row>
-    <row r="26" spans="13:22" x14ac:dyDescent="0.25">
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="70"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="M12" s="57"/>
+      <c r="N12" s="57"/>
+      <c r="O12" s="57"/>
+      <c r="P12" s="58"/>
+      <c r="Q12" s="58"/>
+      <c r="R12" s="58"/>
+      <c r="S12" s="58"/>
+      <c r="T12" s="58"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="29"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="M13" s="46"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="59"/>
+      <c r="T13" s="59"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="48"/>
+      <c r="R14" s="48"/>
+      <c r="S14" s="59"/>
+      <c r="T14" s="59"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="M15" s="46"/>
+      <c r="N15" s="46"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="48"/>
+      <c r="S15" s="59"/>
+      <c r="T15" s="60"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+    </row>
+    <row r="16" spans="1:22" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M16" s="46"/>
+      <c r="N16" s="46"/>
+      <c r="O16" s="47"/>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="48"/>
+      <c r="S16" s="48"/>
+      <c r="T16" s="59"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="29"/>
+    </row>
+    <row r="17" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="47"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="48"/>
+      <c r="R17" s="59"/>
+      <c r="S17" s="59"/>
+      <c r="T17" s="59"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+    </row>
+    <row r="18" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M18" s="46"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="47"/>
+      <c r="P18" s="46"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="48"/>
+      <c r="S18" s="59"/>
+      <c r="T18" s="59"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="29"/>
+    </row>
+    <row r="19" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M19" s="46"/>
+      <c r="N19" s="46"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="46"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="29"/>
+    </row>
+    <row r="20" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M20" s="46"/>
+      <c r="N20" s="46"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="48"/>
+      <c r="Q20" s="48"/>
+      <c r="R20" s="48"/>
+      <c r="S20" s="59"/>
+      <c r="T20" s="59"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+    </row>
+    <row r="21" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M21" s="46"/>
+      <c r="N21" s="46"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="46"/>
+      <c r="Q21" s="46"/>
+      <c r="R21" s="48"/>
+      <c r="S21" s="48"/>
+      <c r="T21" s="59"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="29"/>
+    </row>
+    <row r="22" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M22" s="29"/>
+      <c r="N22" s="61"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="29"/>
+      <c r="Q22" s="29"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="29"/>
+    </row>
+    <row r="23" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+    </row>
+    <row r="24" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="29"/>
+    </row>
+    <row r="25" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+    </row>
+    <row r="26" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2661,67 +2860,67 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D756C6-720B-4AF6-BA44-22676395545C}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="87.5703125" customWidth="1"/>
+    <col min="2" max="2" width="87.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="54" t="s">
+        <v>406</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="66" x14ac:dyDescent="0.3">
+      <c r="A2" s="52" t="s">
+        <v>405</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="52" t="s">
+        <v>410</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="52" t="s">
+        <v>409</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="52" t="s">
         <v>411</v>
       </c>
-      <c r="B1" s="67" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
-        <v>410</v>
-      </c>
-      <c r="B2" s="66" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
-        <v>415</v>
-      </c>
-      <c r="B3" s="66" t="s">
+      <c r="B5" s="53" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="65" t="s">
+    <row r="6" spans="1:2" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="55" t="s">
+        <v>413</v>
+      </c>
+      <c r="B6" s="56" t="s">
         <v>414</v>
       </c>
-      <c r="B4" s="66" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="65" t="s">
-        <v>416</v>
-      </c>
-      <c r="B5" s="66" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="51" x14ac:dyDescent="0.25">
-      <c r="A6" s="68" t="s">
-        <v>418</v>
-      </c>
-      <c r="B6" s="69" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="63"/>
-      <c r="B7" s="63"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="64"/>
-      <c r="B8" s="64"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="50"/>
+      <c r="B7" s="50"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="51"/>
+      <c r="B8" s="51"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2731,81 +2930,81 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD0BCD5-90F5-4339-9647-CB150CEFF8D3}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.109375" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="4" max="4" width="27.5546875" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+    <row r="1" spans="1:5" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A1" s="76" t="s">
+        <v>415</v>
+      </c>
+      <c r="B1" s="76" t="s">
+        <v>416</v>
+      </c>
+      <c r="C1" s="76" t="s">
+        <v>417</v>
+      </c>
+      <c r="D1" s="76" t="s">
+        <v>418</v>
+      </c>
+      <c r="E1" s="77" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="78" t="s">
         <v>420</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B2" s="79" t="s">
         <v>421</v>
       </c>
-      <c r="C1" s="89" t="s">
+      <c r="C2" s="79" t="s">
         <v>422</v>
       </c>
-      <c r="D1" s="89" t="s">
+      <c r="D2" s="79" t="s">
+        <v>421</v>
+      </c>
+      <c r="E2" s="79" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="78" t="s">
         <v>423</v>
       </c>
-      <c r="E1" s="90" t="s">
+      <c r="B3" s="79" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="91" t="s">
+      <c r="C3" s="79" t="s">
         <v>425</v>
       </c>
-      <c r="B2" s="92" t="s">
+      <c r="D3" s="79" t="s">
         <v>426</v>
       </c>
-      <c r="C2" s="92" t="s">
+      <c r="E3" s="79" t="s">
         <v>427</v>
       </c>
-      <c r="D2" s="92" t="s">
-        <v>426</v>
-      </c>
-      <c r="E2" s="92" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="91" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="80" t="s">
         <v>428</v>
       </c>
-      <c r="B3" s="92" t="s">
+      <c r="B4" s="81" t="s">
         <v>429</v>
       </c>
-      <c r="C3" s="92" t="s">
+      <c r="C4" s="81" t="s">
         <v>430</v>
       </c>
-      <c r="D3" s="92" t="s">
+      <c r="D4" s="81" t="s">
         <v>431</v>
       </c>
-      <c r="E3" s="92" t="s">
+      <c r="E4" s="81" t="s">
         <v>432</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="51" x14ac:dyDescent="0.25">
-      <c r="A4" s="93" t="s">
-        <v>433</v>
-      </c>
-      <c r="B4" s="94" t="s">
-        <v>434</v>
-      </c>
-      <c r="C4" s="94" t="s">
-        <v>435</v>
-      </c>
-      <c r="D4" s="94" t="s">
-        <v>436</v>
-      </c>
-      <c r="E4" s="94" t="s">
-        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -2816,313 +3015,319 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAE398DA-232C-4FEE-A95F-A67F85B82E84}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="28.42578125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="30.42578125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="23.42578125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="25.42578125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="20.5546875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="28.44140625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="30.44140625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="26.5546875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.88671875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="23.44140625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="25.44140625" style="6" customWidth="1"/>
     <col min="8" max="8" width="40" style="6" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" style="6" customWidth="1"/>
-    <col min="10" max="10" width="22.42578125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="19.44140625" style="6" customWidth="1"/>
+    <col min="10" max="10" width="22.44140625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="95" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="87" t="s">
         <v>227</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="88" t="s">
         <v>333</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46" t="s">
+      <c r="C1" s="88"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89" t="s">
         <v>342</v>
       </c>
-      <c r="F1" s="46" t="s">
+      <c r="F1" s="89" t="s">
         <v>334</v>
       </c>
-      <c r="G1" s="46" t="s">
+      <c r="G1" s="89" t="s">
         <v>342</v>
       </c>
-      <c r="H1" s="46" t="s">
+      <c r="H1" s="89" t="s">
         <v>341</v>
       </c>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
     </row>
-    <row r="2" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="95" t="s">
-        <v>379</v>
-      </c>
-      <c r="B2" s="8" t="s">
+    <row r="2" spans="1:10" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="87" t="s">
+        <v>375</v>
+      </c>
+      <c r="B2" s="90" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="90" t="s">
+        <v>349</v>
+      </c>
+      <c r="D2" s="91" t="s">
         <v>350</v>
       </c>
-      <c r="D2" s="50" t="s">
-        <v>351</v>
-      </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="92" t="s">
         <v>343</v>
       </c>
-      <c r="F2" s="51"/>
-      <c r="G2" s="52" t="s">
+      <c r="F2" s="92"/>
+      <c r="G2" s="88" t="s">
+        <v>435</v>
+      </c>
+      <c r="H2" s="88"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="87" t="s">
+        <v>228</v>
+      </c>
+      <c r="B3" s="92" t="s">
+        <v>358</v>
+      </c>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="89" t="s">
+        <v>344</v>
+      </c>
+      <c r="G3" s="93" t="s">
         <v>345</v>
       </c>
-      <c r="H2" s="52"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="95" t="s">
-        <v>228</v>
-      </c>
-      <c r="B3" s="51" t="s">
-        <v>359</v>
-      </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="46" t="s">
-        <v>344</v>
-      </c>
-      <c r="G3" s="46" t="s">
-        <v>346</v>
-      </c>
-      <c r="H3" s="46"/>
+      <c r="H3" s="93"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="95" t="s">
+    <row r="4" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="87" t="s">
+        <v>359</v>
+      </c>
+      <c r="B4" s="88" t="s">
+        <v>361</v>
+      </c>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="89" t="s">
+        <v>362</v>
+      </c>
+      <c r="G4" s="90" t="s">
         <v>360</v>
       </c>
-      <c r="B4" s="52" t="s">
-        <v>363</v>
-      </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="46" t="s">
-        <v>364</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="H4" s="46" t="s">
-        <v>361</v>
+      <c r="H4" s="89" t="s">
+        <v>436</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="95" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="87" t="s">
+        <v>346</v>
+      </c>
+      <c r="B5" s="90" t="s">
         <v>347</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="92" t="s">
         <v>229</v>
       </c>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="46" t="s">
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="89" t="s">
         <v>236</v>
       </c>
-      <c r="G5" s="46" t="s">
+      <c r="G5" s="89" t="s">
         <v>229</v>
       </c>
-      <c r="H5" s="46" t="s">
-        <v>365</v>
+      <c r="H5" s="89" t="s">
+        <v>363</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
     </row>
-    <row r="6" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="95" t="s">
+    <row r="6" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="87" t="s">
         <v>336</v>
       </c>
-      <c r="B6" s="46" t="s">
-        <v>349</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>355</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>352</v>
-      </c>
-      <c r="E6" s="46" t="s">
-        <v>366</v>
-      </c>
-      <c r="F6" s="46" t="s">
-        <v>367</v>
-      </c>
-      <c r="G6" s="46" t="s">
+      <c r="B6" s="89" t="s">
+        <v>348</v>
+      </c>
+      <c r="C6" s="89" t="s">
+        <v>354</v>
+      </c>
+      <c r="D6" s="89" t="s">
+        <v>351</v>
+      </c>
+      <c r="E6" s="89" t="s">
+        <v>364</v>
+      </c>
+      <c r="F6" s="89" t="s">
+        <v>365</v>
+      </c>
+      <c r="G6" s="89" t="s">
         <v>335</v>
       </c>
-      <c r="H6" s="47"/>
+      <c r="H6" s="86" t="s">
+        <v>437</v>
+      </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="95" t="s">
+    <row r="7" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="87" t="s">
+        <v>352</v>
+      </c>
+      <c r="B7" s="90" t="s">
         <v>353</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="90" t="s">
+        <v>355</v>
+      </c>
+      <c r="D7" s="90" t="s">
         <v>356</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="89" t="s">
+        <v>323</v>
+      </c>
+      <c r="F7" s="89" t="s">
         <v>357</v>
       </c>
-      <c r="E7" s="46" t="s">
+      <c r="G7" s="89" t="s">
         <v>323</v>
       </c>
-      <c r="F7" s="46" t="s">
-        <v>358</v>
-      </c>
-      <c r="G7" s="46" t="s">
-        <v>323</v>
-      </c>
-      <c r="H7" s="46" t="s">
-        <v>368</v>
+      <c r="H7" s="89" t="s">
+        <v>366</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="95" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="87" t="s">
         <v>337</v>
       </c>
-      <c r="B8" s="52" t="s">
-        <v>369</v>
-      </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52" t="s">
-        <v>370</v>
-      </c>
-      <c r="G8" s="52"/>
-      <c r="H8" s="46" t="s">
-        <v>371</v>
+      <c r="B8" s="88" t="s">
+        <v>367</v>
+      </c>
+      <c r="C8" s="88"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88" t="s">
+        <v>368</v>
+      </c>
+      <c r="G8" s="88"/>
+      <c r="H8" s="89" t="s">
+        <v>433</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="95" t="s">
+    <row r="9" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="87" t="s">
         <v>338</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="90" t="s">
         <v>230</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="90" t="s">
         <v>231</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="90" t="s">
         <v>232</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="90" t="s">
         <v>232</v>
       </c>
-      <c r="F9" s="49" t="s">
-        <v>372</v>
-      </c>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
+      <c r="F9" s="94" t="s">
+        <v>369</v>
+      </c>
+      <c r="G9" s="95"/>
+      <c r="H9" s="95"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="96" t="s">
         <v>339</v>
       </c>
-      <c r="B10" s="53" t="s">
-        <v>375</v>
-      </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="51" t="s">
-        <v>382</v>
-      </c>
-      <c r="G10" s="51" t="s">
-        <v>381</v>
-      </c>
-      <c r="H10" s="52" t="s">
-        <v>373</v>
+      <c r="B10" s="97" t="s">
+        <v>371</v>
+      </c>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
+      <c r="F10" s="92" t="s">
+        <v>377</v>
+      </c>
+      <c r="G10" s="92" t="s">
+        <v>376</v>
+      </c>
+      <c r="H10" s="88" t="s">
+        <v>434</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="96"/>
-      <c r="B11" s="46" t="s">
-        <v>376</v>
-      </c>
-      <c r="C11" s="46" t="s">
-        <v>377</v>
-      </c>
-      <c r="D11" s="46" t="s">
-        <v>377</v>
-      </c>
-      <c r="E11" s="46" t="s">
-        <v>378</v>
-      </c>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="52"/>
+      <c r="B11" s="89" t="s">
+        <v>372</v>
+      </c>
+      <c r="C11" s="89" t="s">
+        <v>373</v>
+      </c>
+      <c r="D11" s="89" t="s">
+        <v>373</v>
+      </c>
+      <c r="E11" s="89" t="s">
+        <v>374</v>
+      </c>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="88"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A12" s="95" t="s">
-        <v>380</v>
-      </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46" t="s">
-        <v>374</v>
-      </c>
-      <c r="G12" s="48">
-        <v>0.95</v>
-      </c>
-      <c r="H12" s="47"/>
+    <row r="12" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="87" t="s">
+        <v>438</v>
+      </c>
+      <c r="B12" s="89"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="89" t="s">
+        <v>370</v>
+      </c>
+      <c r="G12" s="89" t="s">
+        <v>439</v>
+      </c>
+      <c r="H12" s="86" t="s">
+        <v>440</v>
+      </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="95" t="s">
+    <row r="13" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="87" t="s">
         <v>340</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="90" t="s">
         <v>233</v>
       </c>
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="92" t="s">
         <v>234</v>
       </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="8" t="s">
+      <c r="D13" s="92"/>
+      <c r="E13" s="90" t="s">
         <v>235</v>
       </c>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
+      <c r="F13" s="89"/>
+      <c r="G13" s="98" t="s">
+        <v>234</v>
+      </c>
+      <c r="H13" s="98"/>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -3134,7 +3339,7 @@
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -3147,7 +3352,12 @@
       <c r="J15" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A10:A11"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="B10:E10"/>
@@ -3157,34 +3367,1077 @@
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C117A2-91C5-4666-A629-44E9B324BF37}">
+  <dimension ref="A1:H44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.88671875" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="99" t="s">
+        <v>441</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>442</v>
+      </c>
+      <c r="C1" s="99" t="s">
+        <v>443</v>
+      </c>
+      <c r="D1" s="99" t="s">
+        <v>444</v>
+      </c>
+      <c r="E1" s="99" t="s">
+        <v>445</v>
+      </c>
+      <c r="F1" s="99" t="s">
+        <v>446</v>
+      </c>
+      <c r="G1" s="99" t="s">
+        <v>447</v>
+      </c>
+      <c r="H1" s="99" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>10204</v>
+      </c>
+      <c r="D2">
+        <v>9166</v>
+      </c>
+      <c r="E2">
+        <v>1006</v>
+      </c>
+      <c r="F2">
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>10082</v>
+      </c>
+      <c r="D3">
+        <v>9085</v>
+      </c>
+      <c r="E3">
+        <v>965</v>
+      </c>
+      <c r="F3">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>451</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>10453</v>
+      </c>
+      <c r="D4">
+        <v>9393</v>
+      </c>
+      <c r="E4">
+        <v>1026</v>
+      </c>
+      <c r="F4">
+        <v>22</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>452</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>10040</v>
+      </c>
+      <c r="D5">
+        <v>9039</v>
+      </c>
+      <c r="E5">
+        <v>969</v>
+      </c>
+      <c r="F5">
+        <v>22</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>453</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>10705</v>
+      </c>
+      <c r="D6">
+        <v>9632</v>
+      </c>
+      <c r="E6">
+        <v>1036</v>
+      </c>
+      <c r="F6">
+        <v>27</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>454</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>10520</v>
+      </c>
+      <c r="D7">
+        <v>9506</v>
+      </c>
+      <c r="E7">
+        <v>980</v>
+      </c>
+      <c r="F7">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>455</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>33</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>456</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>7926</v>
+      </c>
+      <c r="D9">
+        <v>7127</v>
+      </c>
+      <c r="E9">
+        <v>776</v>
+      </c>
+      <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>457</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>1551</v>
+      </c>
+      <c r="D10">
+        <v>1367</v>
+      </c>
+      <c r="E10">
+        <v>168</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>458</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>53</v>
+      </c>
+      <c r="D11">
+        <v>45</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>459</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>1663</v>
+      </c>
+      <c r="D12">
+        <v>1458</v>
+      </c>
+      <c r="E12">
+        <v>189</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>460</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>1661</v>
+      </c>
+      <c r="D13">
+        <v>1460</v>
+      </c>
+      <c r="E13">
+        <v>185</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>461</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>1627</v>
+      </c>
+      <c r="D14">
+        <v>1434</v>
+      </c>
+      <c r="E14">
+        <v>177</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>462</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>2176</v>
+      </c>
+      <c r="D15">
+        <v>1908</v>
+      </c>
+      <c r="E15">
+        <v>252</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>463</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>1566</v>
+      </c>
+      <c r="D16">
+        <v>1379</v>
+      </c>
+      <c r="E16">
+        <v>171</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>464</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>1638</v>
+      </c>
+      <c r="D17">
+        <v>1442</v>
+      </c>
+      <c r="E17">
+        <v>180</v>
+      </c>
+      <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>465</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>1615</v>
+      </c>
+      <c r="D18">
+        <v>1412</v>
+      </c>
+      <c r="E18">
+        <v>187</v>
+      </c>
+      <c r="F18">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>466</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1547</v>
+      </c>
+      <c r="D19">
+        <v>1368</v>
+      </c>
+      <c r="E19">
+        <v>163</v>
+      </c>
+      <c r="F19">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>467</v>
+      </c>
+      <c r="B20">
+        <v>6</v>
+      </c>
+      <c r="C20">
+        <v>8857</v>
+      </c>
+      <c r="D20">
+        <v>7950</v>
+      </c>
+      <c r="E20">
+        <v>870</v>
+      </c>
+      <c r="F20">
+        <v>24</v>
+      </c>
+      <c r="G20">
+        <v>7</v>
+      </c>
+      <c r="H20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>468</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>1586</v>
+      </c>
+      <c r="D21">
+        <v>1400</v>
+      </c>
+      <c r="E21">
+        <v>170</v>
+      </c>
+      <c r="F21">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>469</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>1539</v>
+      </c>
+      <c r="D22">
+        <v>1358</v>
+      </c>
+      <c r="E22">
+        <v>165</v>
+      </c>
+      <c r="F22">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>470</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>1626</v>
+      </c>
+      <c r="D23">
+        <v>1422</v>
+      </c>
+      <c r="E23">
+        <v>188</v>
+      </c>
+      <c r="F23">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>471</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <v>1714</v>
+      </c>
+      <c r="D24">
+        <v>1490</v>
+      </c>
+      <c r="E24">
+        <v>209</v>
+      </c>
+      <c r="F24">
+        <v>9</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>472</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>1473</v>
+      </c>
+      <c r="D25">
+        <v>1303</v>
+      </c>
+      <c r="E25">
+        <v>154</v>
+      </c>
+      <c r="F25">
+        <v>10</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>473</v>
+      </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26">
+        <v>1780</v>
+      </c>
+      <c r="D26">
+        <v>1557</v>
+      </c>
+      <c r="E26">
+        <v>208</v>
+      </c>
+      <c r="F26">
+        <v>10</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>474</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>61</v>
+      </c>
+      <c r="D27">
+        <v>53</v>
+      </c>
+      <c r="E27">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>475</v>
+      </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28">
+        <v>61</v>
+      </c>
+      <c r="D28">
+        <v>55</v>
+      </c>
+      <c r="E28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>476</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29">
+        <v>53</v>
+      </c>
+      <c r="D29">
+        <v>46</v>
+      </c>
+      <c r="E29">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>477</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30">
+        <v>9727</v>
+      </c>
+      <c r="D30">
+        <v>8707</v>
+      </c>
+      <c r="E30">
+        <v>986</v>
+      </c>
+      <c r="F30">
+        <v>23</v>
+      </c>
+      <c r="G30">
+        <v>3</v>
+      </c>
+      <c r="H30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>478</v>
+      </c>
+      <c r="B31">
+        <v>4</v>
+      </c>
+      <c r="C31">
+        <v>9817</v>
+      </c>
+      <c r="D31">
+        <v>8780</v>
+      </c>
+      <c r="E31">
+        <v>1002</v>
+      </c>
+      <c r="F31">
+        <v>22</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+      <c r="H31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>479</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32">
+        <v>42</v>
+      </c>
+      <c r="D32">
+        <v>36</v>
+      </c>
+      <c r="E32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>480</v>
+      </c>
+      <c r="B33">
+        <v>4</v>
+      </c>
+      <c r="C33">
+        <v>9646</v>
+      </c>
+      <c r="D33">
+        <v>8640</v>
+      </c>
+      <c r="E33">
+        <v>968</v>
+      </c>
+      <c r="F33">
+        <v>23</v>
+      </c>
+      <c r="G33">
+        <v>6</v>
+      </c>
+      <c r="H33">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>481</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34">
+        <v>53</v>
+      </c>
+      <c r="D34">
+        <v>47</v>
+      </c>
+      <c r="E34">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>482</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35">
+        <v>10071</v>
+      </c>
+      <c r="D35">
+        <v>8990</v>
+      </c>
+      <c r="E35">
+        <v>1043</v>
+      </c>
+      <c r="F35">
+        <v>22</v>
+      </c>
+      <c r="G35">
+        <v>6</v>
+      </c>
+      <c r="H35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>483</v>
+      </c>
+      <c r="B36">
+        <v>4</v>
+      </c>
+      <c r="C36">
+        <v>9484</v>
+      </c>
+      <c r="D36">
+        <v>8508</v>
+      </c>
+      <c r="E36">
+        <v>943</v>
+      </c>
+      <c r="F36">
+        <v>21</v>
+      </c>
+      <c r="G36">
+        <v>4</v>
+      </c>
+      <c r="H36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>484</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37">
+        <v>92</v>
+      </c>
+      <c r="D37">
+        <v>73</v>
+      </c>
+      <c r="E37">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>485</v>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38">
+        <v>6100</v>
+      </c>
+      <c r="D38">
+        <v>5444</v>
+      </c>
+      <c r="E38">
+        <v>627</v>
+      </c>
+      <c r="F38">
+        <v>16</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+      <c r="H38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>486</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39">
+        <v>7072</v>
+      </c>
+      <c r="D39">
+        <v>6252</v>
+      </c>
+      <c r="E39">
+        <v>795</v>
+      </c>
+      <c r="F39">
+        <v>13</v>
+      </c>
+      <c r="G39">
+        <v>5</v>
+      </c>
+      <c r="H39">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>487</v>
+      </c>
+      <c r="B40">
+        <v>2</v>
+      </c>
+      <c r="C40">
+        <v>35</v>
+      </c>
+      <c r="D40">
+        <v>29</v>
+      </c>
+      <c r="E40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>488</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="C41">
+        <v>44</v>
+      </c>
+      <c r="D41">
+        <v>36</v>
+      </c>
+      <c r="E41">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>489</v>
+      </c>
+      <c r="B42">
+        <v>2</v>
+      </c>
+      <c r="C42">
+        <v>116</v>
+      </c>
+      <c r="D42">
+        <v>102</v>
+      </c>
+      <c r="E42">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>490</v>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43">
+        <v>206</v>
+      </c>
+      <c r="D43">
+        <v>175</v>
+      </c>
+      <c r="E43">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>491</v>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44">
+        <v>46</v>
+      </c>
+      <c r="D44">
+        <v>39</v>
+      </c>
+      <c r="E44">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F811F764-2817-42B1-BB85-AB1C44C4F3B3}">
   <dimension ref="A1:V65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" customWidth="1"/>
-    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5546875" customWidth="1"/>
+    <col min="2" max="2" width="36.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>43</v>
       </c>
@@ -3207,7 +4460,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>188</v>
       </c>
@@ -3234,7 +4487,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>163</v>
       </c>
@@ -3261,7 +4514,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>176</v>
       </c>
@@ -3288,7 +4541,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>182</v>
       </c>
@@ -3315,7 +4568,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>185</v>
       </c>
@@ -3341,7 +4594,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>192</v>
       </c>
@@ -3368,7 +4621,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>139</v>
       </c>
@@ -3395,7 +4648,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>136</v>
       </c>
@@ -3422,7 +4675,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>104</v>
       </c>
@@ -3448,7 +4701,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -3475,7 +4728,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>170</v>
       </c>
@@ -3502,7 +4755,7 @@
       <c r="J12" s="1"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>158</v>
       </c>
@@ -3529,7 +4782,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -3555,7 +4808,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>80</v>
       </c>
@@ -3580,7 +4833,7 @@
       <c r="J15" s="1"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>152</v>
       </c>
@@ -3607,7 +4860,7 @@
       <c r="J16" s="1"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>153</v>
       </c>
@@ -3634,7 +4887,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>56</v>
       </c>
@@ -3658,7 +4911,7 @@
       </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>88</v>
       </c>
@@ -3685,7 +4938,7 @@
       <c r="J19" s="1"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>127</v>
       </c>
@@ -3712,7 +4965,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>123</v>
       </c>
@@ -3739,7 +4992,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>142</v>
       </c>
@@ -3765,7 +5018,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>95</v>
       </c>
@@ -3791,7 +5044,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>169</v>
       </c>
@@ -3818,7 +5071,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>195</v>
       </c>
@@ -3841,7 +5094,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -3871,7 +5124,7 @@
       <c r="U26" s="1"/>
       <c r="V26" s="2"/>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>73</v>
       </c>
@@ -3897,7 +5150,7 @@
       <c r="J27" s="1"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>84</v>
       </c>
@@ -3925,7 +5178,7 @@
       <c r="U28" s="1"/>
       <c r="V28" s="2"/>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>196</v>
       </c>
@@ -3948,7 +5201,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>157</v>
       </c>
@@ -3978,7 +5231,7 @@
       <c r="U30" s="1"/>
       <c r="V30" s="2"/>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>130</v>
       </c>
@@ -4005,7 +5258,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>180</v>
       </c>
@@ -4036,7 +5289,7 @@
       <c r="U32" s="1"/>
       <c r="V32" s="2"/>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>117</v>
       </c>
@@ -4063,7 +5316,7 @@
       <c r="J33" s="1"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>114</v>
       </c>
@@ -4093,7 +5346,7 @@
       <c r="U34" s="1"/>
       <c r="V34" s="2"/>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -4119,7 +5372,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>85</v>
       </c>
@@ -4146,7 +5399,7 @@
       <c r="J36" s="1"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>171</v>
       </c>
@@ -4173,7 +5426,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>75</v>
       </c>
@@ -4199,7 +5452,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>160</v>
       </c>
@@ -4226,7 +5479,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>140</v>
       </c>
@@ -4253,7 +5506,7 @@
       <c r="J40" s="1"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>108</v>
       </c>
@@ -4278,7 +5531,7 @@
       <c r="J41" s="1"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>120</v>
       </c>
@@ -4305,7 +5558,7 @@
       <c r="J42" s="1"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>53</v>
       </c>
@@ -4332,7 +5585,7 @@
       <c r="J43" s="1"/>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>126</v>
       </c>
@@ -4359,7 +5612,7 @@
       <c r="J44" s="1"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>167</v>
       </c>
@@ -4386,7 +5639,7 @@
       <c r="J45" s="1"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>133</v>
       </c>
@@ -4412,7 +5665,7 @@
       <c r="J46" s="1"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>77</v>
       </c>
@@ -4438,7 +5691,7 @@
       <c r="J47" s="1"/>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>197</v>
       </c>
@@ -4461,7 +5714,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>181</v>
       </c>
@@ -4488,7 +5741,7 @@
       <c r="J49" s="1"/>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>145</v>
       </c>
@@ -4515,7 +5768,7 @@
       <c r="J50" s="1"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>148</v>
       </c>
@@ -4542,7 +5795,7 @@
       <c r="J51" s="1"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>149</v>
       </c>
@@ -4569,7 +5822,7 @@
       <c r="J52" s="1"/>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>150</v>
       </c>
@@ -4596,7 +5849,7 @@
       <c r="J53" s="1"/>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>151</v>
       </c>
@@ -4622,7 +5875,7 @@
       <c r="J54" s="1"/>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>194</v>
       </c>
@@ -4646,7 +5899,7 @@
       </c>
       <c r="K55" s="1"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>174</v>
       </c>
@@ -4673,7 +5926,7 @@
       <c r="J56" s="1"/>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>155</v>
       </c>
@@ -4700,7 +5953,7 @@
       <c r="J57" s="1"/>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>98</v>
       </c>
@@ -4727,7 +5980,7 @@
       <c r="J58" s="1"/>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>101</v>
       </c>
@@ -4754,7 +6007,7 @@
       <c r="J59" s="1"/>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>49</v>
       </c>
@@ -4780,7 +6033,7 @@
       <c r="I60" s="4"/>
       <c r="J60" s="1"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>81</v>
       </c>
@@ -4806,7 +6059,7 @@
       <c r="J61" s="1"/>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>59</v>
       </c>
@@ -4833,7 +6086,7 @@
       <c r="J62" s="1"/>
       <c r="K62" s="2"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>128</v>
       </c>
@@ -4860,7 +6113,7 @@
       <c r="J63" s="1"/>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>111</v>
       </c>
@@ -4887,7 +6140,7 @@
       <c r="J64" s="1"/>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>129</v>
       </c>
@@ -4936,316 +6189,316 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA0C9990-F6EB-4079-9807-3DC74FA9CD4F}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="3" max="4" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="21"/>
-      <c r="B1" s="54" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="20"/>
+      <c r="B1" s="82" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="19" t="s">
         <v>302</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="19" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="11" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="11" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="11" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>269</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="22" t="s">
         <v>279</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="23" t="s">
         <v>286</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="17"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F15" s="13"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F16" s="13"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-    </row>
-    <row r="17" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F17" s="13"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-    </row>
-    <row r="18" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F18" s="13"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-    </row>
-    <row r="19" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F19" s="13"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-    </row>
-    <row r="20" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F20" s="13"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-    </row>
-    <row r="21" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F21" s="13"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-    </row>
-    <row r="22" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-    </row>
-    <row r="23" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-    </row>
-    <row r="24" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-    </row>
-    <row r="25" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="H11" s="15"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="16"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="16"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F15" s="12"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F16" s="12"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+    </row>
+    <row r="17" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F17" s="12"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+    </row>
+    <row r="18" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F18" s="12"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+    </row>
+    <row r="19" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F19" s="12"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+    </row>
+    <row r="20" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F20" s="12"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+    </row>
+    <row r="21" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F21" s="12"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+    </row>
+    <row r="22" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+    </row>
+    <row r="23" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+    </row>
+    <row r="24" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+    </row>
+    <row r="25" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5255,17 +6508,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9DE55F8-E723-4EB4-9908-92E8B4327F36}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>304</v>
       </c>
@@ -5285,7 +6538,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>303</v>
       </c>
@@ -5299,8 +6552,8 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="24">
         <v>0.01</v>
       </c>
       <c r="B3" t="s">
@@ -5313,76 +6566,76 @@
         <v>307</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="24">
         <v>1E-3</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="25">
         <v>320</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="25">
         <v>150</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="25">
         <v>322</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="24">
         <v>1E-4</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="25">
         <v>106</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="25">
         <v>61</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="25">
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="24">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="25">
         <v>49</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="25">
         <v>6</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="25">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>309</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="25">
         <f>(B4/(A4*F1)+B5/(A5*F1)+B6/(A6*F1))/3</f>
         <v>20933333.333333332</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="25">
         <f>(C4/(A4*F1)+C5/(A5*F1)+C6/(A6*F1))/3</f>
         <v>4533333.333333333</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="25">
         <f>(D4/(A4*F1)+D5/(A5*F1)+D6/(A6*F1))/3</f>
         <v>8606666.666666666</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>310</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <v>20933333.333333332</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <v>4533333.333333333</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="26">
         <v>8606666.666666666</v>
       </c>
     </row>
@@ -5391,78 +6644,78 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12C9C68-1E13-46D6-A886-AFAC0C6F13C8}">
   <dimension ref="A1:M1048576"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" style="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" style="39" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" style="38" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.42578125" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" style="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="37" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" style="37" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.44140625" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>312</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="33" t="s">
         <v>313</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="36" t="s">
         <v>331</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="41" t="s">
         <v>323</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="33" t="s">
         <v>327</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="32" t="s">
         <v>322</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="32" t="s">
         <v>304</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="32" t="s">
         <v>305</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="32" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="83" t="s">
         <v>304</v>
       </c>
-      <c r="B2" s="28">
+      <c r="B2" s="27">
         <v>69</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D2" s="29">
+      <c r="D2" s="28">
         <v>1.98</v>
       </c>
-      <c r="E2" s="29"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="I2" s="41" t="s">
+      <c r="E2" s="28"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="I2" s="40" t="s">
         <v>317</v>
       </c>
       <c r="J2" s="6">
@@ -5482,22 +6735,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="55"/>
-      <c r="B3" s="28">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="83"/>
+      <c r="B3" s="27">
         <v>70</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="28">
         <v>1.82</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="41" t="s">
+      <c r="E3" s="28"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="40" t="s">
         <v>318</v>
       </c>
       <c r="J3" s="6">
@@ -5517,17 +6770,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="55"/>
-      <c r="B4" s="28">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="83"/>
+      <c r="B4" s="27">
         <v>71</v>
       </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="41" t="s">
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="40" t="s">
         <v>316</v>
       </c>
       <c r="J4" s="6">
@@ -5547,22 +6800,22 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="55"/>
-      <c r="B5" s="28">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="83"/>
+      <c r="B5" s="27">
         <v>72</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="28">
         <v>1.37</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="28" t="s">
+      <c r="E5" s="28"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="27" t="s">
         <v>319</v>
       </c>
       <c r="J5" s="6">
@@ -5582,2946 +6835,2946 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="55"/>
-      <c r="B6" s="28">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="83"/>
+      <c r="B6" s="27">
         <v>73</v>
       </c>
-      <c r="C6" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D6" s="29">
+      <c r="C6" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D6" s="28">
         <v>2.0099999999999998</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="29" t="s">
         <v>325</v>
       </c>
-      <c r="G6" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="H6" s="30"/>
-      <c r="I6" s="37" t="s">
+      <c r="G6" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="H6" s="29"/>
+      <c r="I6" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="J6" s="42">
+      <c r="J6" s="41">
         <f t="shared" ref="J6" si="3">COUNTIF($C$2:$C$191,I6)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="42">
+      <c r="K6" s="41">
         <f>COUNTIF($C$2:$C$58,"")</f>
         <v>4</v>
       </c>
-      <c r="L6" s="42">
+      <c r="L6" s="41">
         <f>COUNTIF($C$59:$C$128,"")</f>
         <v>19</v>
       </c>
-      <c r="M6" s="42">
+      <c r="M6" s="41">
         <f>COUNTIF($C$129:$C$191,"")</f>
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="55"/>
-      <c r="B7" s="28">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="83"/>
+      <c r="B7" s="27">
         <v>74</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="28">
         <v>2.14</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="55"/>
-      <c r="B8" s="28">
+      <c r="E7" s="28"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="83"/>
+      <c r="B8" s="27">
         <v>75</v>
       </c>
-      <c r="C8" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D8" s="29">
+      <c r="C8" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D8" s="28">
         <v>1.99</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G8" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="55"/>
-      <c r="B9" s="28">
+      <c r="G8" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="83"/>
+      <c r="B9" s="27">
         <v>76</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>1.9</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30">
+      <c r="E9" s="28"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29">
         <f>COUNTIF(G:G,G6)</f>
         <v>45</v>
       </c>
-      <c r="J9" s="30"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="55"/>
-      <c r="B10" s="28">
+      <c r="J9" s="29"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="83"/>
+      <c r="B10" s="27">
         <v>77</v>
       </c>
-      <c r="C10" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D10" s="29">
+      <c r="C10" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D10" s="28">
         <v>2</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G10" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="55"/>
-      <c r="B11" s="28">
+      <c r="G10" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="83"/>
+      <c r="B11" s="27">
         <v>78</v>
       </c>
-      <c r="C11" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D11" s="29">
+      <c r="C11" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D11" s="28">
         <v>2.0499999999999998</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="30" t="s">
+      <c r="E11" s="28"/>
+      <c r="F11" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G11" s="39"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="55"/>
-      <c r="B12" s="28">
+      <c r="G11" s="38"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="83"/>
+      <c r="B12" s="27">
         <v>79</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="28">
         <v>2.0299999999999998</v>
       </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="55"/>
-      <c r="B13" s="28">
+      <c r="E12" s="28"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="83"/>
+      <c r="B13" s="27">
         <v>80</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="28">
         <v>1.85</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="55"/>
-      <c r="B14" s="28">
+      <c r="E13" s="28"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="83"/>
+      <c r="B14" s="27">
         <v>81</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="28">
         <v>2.0099999999999998</v>
       </c>
-      <c r="E14" s="29"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="55"/>
-      <c r="B15" s="28">
+      <c r="E14" s="28"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="83"/>
+      <c r="B15" s="27">
         <v>82</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="28">
         <v>2.0099999999999998</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="55"/>
-      <c r="B16" s="28">
+      <c r="E15" s="28"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="83"/>
+      <c r="B16" s="27">
         <v>83</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="28">
         <v>1.94</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="55"/>
-      <c r="B17" s="28">
+      <c r="E16" s="28"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="83"/>
+      <c r="B17" s="27">
         <v>84</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="28">
         <v>2.0699999999999998</v>
       </c>
-      <c r="E17" s="29"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="55"/>
-      <c r="B18" s="28">
+      <c r="E17" s="28"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="83"/>
+      <c r="B18" s="27">
         <v>85</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="28">
         <v>1.45</v>
       </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="55"/>
-      <c r="B19" s="28">
+      <c r="E18" s="28"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="83"/>
+      <c r="B19" s="27">
         <v>86</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="28">
         <v>1.79</v>
       </c>
-      <c r="E19" s="29"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="55"/>
-      <c r="B20" s="28">
+      <c r="E19" s="28"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="83"/>
+      <c r="B20" s="27">
         <v>87</v>
       </c>
-      <c r="C20" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D20" s="29">
+      <c r="C20" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D20" s="28">
         <v>1.85</v>
       </c>
-      <c r="E20" s="29"/>
-      <c r="F20" s="30" t="s">
+      <c r="E20" s="28"/>
+      <c r="F20" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G20" s="39"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="55"/>
-      <c r="B21" s="28">
+      <c r="G20" s="38"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="83"/>
+      <c r="B21" s="27">
         <v>88</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="28">
         <v>1.32</v>
       </c>
-      <c r="E21" s="29"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="55"/>
-      <c r="B22" s="28">
+      <c r="E21" s="28"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="83"/>
+      <c r="B22" s="27">
         <v>89</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="28">
         <v>2.21</v>
       </c>
-      <c r="E22" s="29"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="55"/>
-      <c r="B23" s="28">
+      <c r="E22" s="28"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="83"/>
+      <c r="B23" s="27">
         <v>90</v>
       </c>
-      <c r="C23" s="39" t="s">
+      <c r="C23" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="28">
         <v>1.99</v>
       </c>
-      <c r="E23" s="29"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="55"/>
-      <c r="B24" s="28">
+      <c r="E23" s="28"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="83"/>
+      <c r="B24" s="27">
         <v>91</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="28">
         <v>1.97</v>
       </c>
-      <c r="E24" s="29"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="55"/>
-      <c r="B25" s="28">
+      <c r="E24" s="28"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="83"/>
+      <c r="B25" s="27">
         <v>92</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="28">
         <v>1.39</v>
       </c>
-      <c r="E25" s="29"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="55"/>
-      <c r="B26" s="28">
+      <c r="E25" s="28"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="83"/>
+      <c r="B26" s="27">
         <v>93</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="28">
         <v>2.14</v>
       </c>
-      <c r="E26" s="29"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="55"/>
-      <c r="B27" s="28">
+      <c r="E26" s="28"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="83"/>
+      <c r="B27" s="27">
         <v>94</v>
       </c>
-      <c r="C27" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D27" s="29">
+      <c r="C27" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D27" s="28">
         <v>1.99</v>
       </c>
-      <c r="E27" s="29" t="s">
+      <c r="E27" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F27" s="30" t="s">
+      <c r="F27" s="29" t="s">
         <v>325</v>
       </c>
-      <c r="G27" s="39" t="s">
+      <c r="G27" s="38" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="55"/>
-      <c r="B28" s="28">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="83"/>
+      <c r="B28" s="27">
         <v>95</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="28">
         <v>1.95</v>
       </c>
-      <c r="E28" s="29"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="55"/>
-      <c r="B29" s="28">
+      <c r="E28" s="28"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="83"/>
+      <c r="B29" s="27">
         <v>96</v>
       </c>
-      <c r="C29" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D29" s="29">
+      <c r="C29" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D29" s="28">
         <v>2.02</v>
       </c>
-      <c r="E29" s="29"/>
-      <c r="F29" s="30" t="s">
+      <c r="E29" s="28"/>
+      <c r="F29" s="29" t="s">
         <v>330</v>
       </c>
-      <c r="G29" s="39"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="55"/>
-      <c r="B30" s="28">
+      <c r="G29" s="38"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="83"/>
+      <c r="B30" s="27">
         <v>97</v>
       </c>
-      <c r="C30" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D30" s="29">
+      <c r="C30" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D30" s="28">
         <v>1.92</v>
       </c>
-      <c r="E30" s="29" t="s">
+      <c r="E30" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F30" s="30" t="s">
+      <c r="F30" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G30" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="55"/>
-      <c r="B31" s="28">
+      <c r="G30" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="83"/>
+      <c r="B31" s="27">
         <v>98</v>
       </c>
-      <c r="C31" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D31" s="29">
+      <c r="C31" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D31" s="28">
         <v>2.08</v>
       </c>
-      <c r="E31" s="29" t="s">
+      <c r="E31" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F31" s="30" t="s">
+      <c r="F31" s="29" t="s">
         <v>325</v>
       </c>
-      <c r="G31" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="55"/>
-      <c r="B32" s="28">
+      <c r="G31" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="83"/>
+      <c r="B32" s="27">
         <v>99</v>
       </c>
-      <c r="C32" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D32" s="29">
+      <c r="C32" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D32" s="28">
         <v>2.0699999999999998</v>
       </c>
-      <c r="E32" s="29"/>
-      <c r="F32" s="30" t="s">
+      <c r="E32" s="28"/>
+      <c r="F32" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G32" s="39"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="55"/>
-      <c r="B33" s="28">
+      <c r="G32" s="38"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="83"/>
+      <c r="B33" s="27">
         <v>100</v>
       </c>
-      <c r="C33" s="39" t="s">
+      <c r="C33" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="28">
         <v>1.72</v>
       </c>
-      <c r="E33" s="29"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="55"/>
-      <c r="B34" s="28">
+      <c r="E33" s="28"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="83"/>
+      <c r="B34" s="27">
         <v>101</v>
       </c>
-      <c r="C34" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D34" s="29">
+      <c r="C34" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D34" s="28">
         <v>2.0699999999999998</v>
       </c>
-      <c r="E34" s="29"/>
-      <c r="F34" s="30" t="s">
+      <c r="E34" s="28"/>
+      <c r="F34" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G34" s="39"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="55"/>
-      <c r="B35" s="28">
+      <c r="G34" s="38"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="83"/>
+      <c r="B35" s="27">
         <v>102</v>
       </c>
-      <c r="C35" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D35" s="29">
+      <c r="C35" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D35" s="28">
         <v>2</v>
       </c>
-      <c r="E35" s="29" t="s">
+      <c r="E35" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F35" s="30" t="s">
+      <c r="F35" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G35" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="55"/>
-      <c r="B36" s="28">
+      <c r="G35" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="83"/>
+      <c r="B36" s="27">
         <v>103</v>
       </c>
-      <c r="C36" s="39" t="s">
+      <c r="C36" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D36" s="29">
+      <c r="D36" s="28">
         <v>1.84</v>
       </c>
-      <c r="E36" s="29"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="55"/>
-      <c r="B37" s="28">
+      <c r="E36" s="28"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="83"/>
+      <c r="B37" s="27">
         <v>104</v>
       </c>
-      <c r="C37" s="39" t="s">
+      <c r="C37" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D37" s="29">
+      <c r="D37" s="28">
         <v>2.08</v>
       </c>
-      <c r="E37" s="29"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="55"/>
-      <c r="B38" s="28">
+      <c r="E37" s="28"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="83"/>
+      <c r="B38" s="27">
         <v>105</v>
       </c>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="55"/>
-      <c r="B39" s="28">
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="83"/>
+      <c r="B39" s="27">
         <v>106</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D39" s="29">
+      <c r="D39" s="28">
         <v>1.32</v>
       </c>
-      <c r="E39" s="29"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="55"/>
-      <c r="B40" s="28">
+      <c r="E39" s="28"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="83"/>
+      <c r="B40" s="27">
         <v>107</v>
       </c>
-      <c r="C40" s="39" t="s">
+      <c r="C40" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D40" s="29">
+      <c r="D40" s="28">
         <v>2.06</v>
       </c>
-      <c r="E40" s="29"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="55"/>
-      <c r="B41" s="28">
+      <c r="E40" s="28"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="83"/>
+      <c r="B41" s="27">
         <v>108</v>
       </c>
-      <c r="C41" s="39" t="s">
+      <c r="C41" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="28">
         <v>2.0299999999999998</v>
       </c>
-      <c r="E41" s="29"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="55"/>
-      <c r="B42" s="28">
+      <c r="E41" s="28"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="83"/>
+      <c r="B42" s="27">
         <v>109</v>
       </c>
-      <c r="C42" s="39" t="s">
+      <c r="C42" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D42" s="29">
+      <c r="D42" s="28">
         <v>2.11</v>
       </c>
-      <c r="E42" s="29"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="55"/>
-      <c r="B43" s="28">
+      <c r="E42" s="28"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="83"/>
+      <c r="B43" s="27">
         <v>110</v>
       </c>
-      <c r="C43" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D43" s="29">
+      <c r="C43" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D43" s="28">
         <v>2.06</v>
       </c>
-      <c r="E43" s="29"/>
-      <c r="F43" s="30" t="s">
+      <c r="E43" s="28"/>
+      <c r="F43" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G43" s="39"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="55"/>
-      <c r="B44" s="28">
+      <c r="G43" s="38"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="83"/>
+      <c r="B44" s="27">
         <v>111</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D44" s="29">
+      <c r="D44" s="28">
         <v>1.54</v>
       </c>
-      <c r="E44" s="29"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="55"/>
-      <c r="B45" s="28">
+      <c r="E44" s="28"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="83"/>
+      <c r="B45" s="27">
         <v>112</v>
       </c>
-      <c r="C45" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D45" s="29">
+      <c r="C45" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D45" s="28">
         <v>2.14</v>
       </c>
-      <c r="E45" s="29"/>
-      <c r="F45" s="30" t="s">
+      <c r="E45" s="28"/>
+      <c r="F45" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G45" s="39"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="55"/>
-      <c r="B46" s="28">
+      <c r="G45" s="38"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="83"/>
+      <c r="B46" s="27">
         <v>113</v>
       </c>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="55"/>
-      <c r="B47" s="28">
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="83"/>
+      <c r="B47" s="27">
         <v>114</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D47" s="29">
+      <c r="D47" s="28">
         <v>1.57</v>
       </c>
-      <c r="E47" s="29"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="55"/>
-      <c r="B48" s="28">
+      <c r="E47" s="28"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="83"/>
+      <c r="B48" s="27">
         <v>115</v>
       </c>
-      <c r="C48" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D48" s="29">
+      <c r="C48" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D48" s="28">
         <v>1.97</v>
       </c>
-      <c r="E48" s="29"/>
-      <c r="F48" s="30" t="s">
+      <c r="E48" s="28"/>
+      <c r="F48" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G48" s="39"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="55"/>
-      <c r="B49" s="28">
+      <c r="G48" s="38"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="83"/>
+      <c r="B49" s="27">
         <v>116</v>
       </c>
-      <c r="C49" s="39" t="s">
+      <c r="C49" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D49" s="29">
+      <c r="D49" s="28">
         <v>1.95</v>
       </c>
-      <c r="E49" s="29"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="55"/>
-      <c r="B50" s="28">
+      <c r="E49" s="28"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="83"/>
+      <c r="B50" s="27">
         <v>117</v>
       </c>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="30"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="55"/>
-      <c r="B51" s="28">
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="29"/>
+      <c r="G50" s="29"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="83"/>
+      <c r="B51" s="27">
         <v>118</v>
       </c>
-      <c r="C51" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D51" s="29">
+      <c r="C51" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D51" s="28">
         <v>1.85</v>
       </c>
-      <c r="E51" s="29" t="s">
+      <c r="E51" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F51" s="30" t="s">
+      <c r="F51" s="29" t="s">
         <v>325</v>
       </c>
-      <c r="G51" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="55"/>
-      <c r="B52" s="28">
+      <c r="G51" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="83"/>
+      <c r="B52" s="27">
         <v>119</v>
       </c>
-      <c r="C52" s="39" t="s">
+      <c r="C52" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="D52" s="29">
+      <c r="D52" s="28">
         <v>1.76</v>
       </c>
-      <c r="E52" s="29"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="55"/>
-      <c r="B53" s="28">
+      <c r="E52" s="28"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="83"/>
+      <c r="B53" s="27">
         <v>120</v>
       </c>
-      <c r="C53" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D53" s="29">
+      <c r="C53" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D53" s="28">
         <v>2.0099999999999998</v>
       </c>
-      <c r="E53" s="29"/>
-      <c r="F53" s="30" t="s">
+      <c r="E53" s="28"/>
+      <c r="F53" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G53" s="39"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="55"/>
-      <c r="B54" s="28">
+      <c r="G53" s="38"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="83"/>
+      <c r="B54" s="27">
         <v>121</v>
       </c>
-      <c r="C54" s="39" t="s">
+      <c r="C54" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D54" s="29">
+      <c r="D54" s="28">
         <v>1.84</v>
       </c>
-      <c r="E54" s="29"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="55"/>
-      <c r="B55" s="28">
+      <c r="E54" s="28"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="83"/>
+      <c r="B55" s="27">
         <v>123</v>
       </c>
-      <c r="C55" s="39" t="s">
+      <c r="C55" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D55" s="29">
+      <c r="D55" s="28">
         <v>1.95</v>
       </c>
-      <c r="E55" s="29"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="55"/>
-      <c r="B56" s="28">
+      <c r="E55" s="28"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="83"/>
+      <c r="B56" s="27">
         <v>124</v>
       </c>
-      <c r="C56" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D56" s="29">
+      <c r="C56" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D56" s="28">
         <v>1.92</v>
       </c>
-      <c r="E56" s="29" t="s">
+      <c r="E56" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F56" s="30" t="s">
+      <c r="F56" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G56" s="39" t="s">
+      <c r="G56" s="38" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="55"/>
-      <c r="B57" s="28">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="83"/>
+      <c r="B57" s="27">
         <v>125</v>
       </c>
-      <c r="C57" s="39" t="s">
+      <c r="C57" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D57" s="29">
+      <c r="D57" s="28">
         <v>2.0099999999999998</v>
       </c>
-      <c r="E57" s="29"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="30"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="56"/>
-      <c r="B58" s="37">
+      <c r="E57" s="28"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="84"/>
+      <c r="B58" s="36">
         <v>126</v>
       </c>
-      <c r="C58" s="40" t="s">
-        <v>316</v>
-      </c>
-      <c r="D58" s="36">
+      <c r="C58" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="D58" s="35">
         <v>2.08</v>
       </c>
-      <c r="E58" s="36" t="s">
+      <c r="E58" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="F58" s="43" t="s">
+      <c r="F58" s="42" t="s">
         <v>324</v>
       </c>
-      <c r="G58" s="40" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="55" t="s">
+      <c r="G58" s="39" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="83" t="s">
         <v>305</v>
       </c>
-      <c r="B59" s="28">
+      <c r="B59" s="27">
         <v>127</v>
       </c>
-      <c r="C59" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D59" s="29">
+      <c r="C59" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D59" s="28">
         <v>1.71</v>
       </c>
-      <c r="E59" s="29"/>
-      <c r="F59" s="30" t="s">
+      <c r="E59" s="28"/>
+      <c r="F59" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G59" s="39"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="55"/>
-      <c r="B60" s="28">
+      <c r="G59" s="38"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="83"/>
+      <c r="B60" s="27">
         <v>128</v>
       </c>
-      <c r="C60" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D60" s="29">
+      <c r="C60" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D60" s="28">
         <v>1.99</v>
       </c>
-      <c r="E60" s="29"/>
-      <c r="F60" s="30" t="s">
+      <c r="E60" s="28"/>
+      <c r="F60" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G60" s="39"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="55"/>
-      <c r="B61" s="28">
+      <c r="G60" s="38"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="83"/>
+      <c r="B61" s="27">
         <v>129</v>
       </c>
-      <c r="C61" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D61" s="29">
+      <c r="C61" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D61" s="28">
         <v>1.96</v>
       </c>
-      <c r="E61" s="29"/>
-      <c r="F61" s="30" t="s">
+      <c r="E61" s="28"/>
+      <c r="F61" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G61" s="39"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="55"/>
-      <c r="B62" s="28">
+      <c r="G61" s="38"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="83"/>
+      <c r="B62" s="27">
         <v>130</v>
       </c>
-      <c r="C62" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D62" s="29">
+      <c r="C62" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D62" s="28">
         <v>2.04</v>
       </c>
-      <c r="E62" s="29"/>
-      <c r="F62" s="29" t="s">
+      <c r="E62" s="28"/>
+      <c r="F62" s="28" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="55"/>
-      <c r="B63" s="28">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="83"/>
+      <c r="B63" s="27">
         <v>131</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D63" s="29">
+      <c r="D63" s="28">
         <v>1.3</v>
       </c>
-      <c r="E63" s="29"/>
-      <c r="F63" s="30"/>
-      <c r="G63" s="30"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="55"/>
-      <c r="B64" s="28">
+      <c r="E63" s="28"/>
+      <c r="F63" s="29"/>
+      <c r="G63" s="29"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="83"/>
+      <c r="B64" s="27">
         <v>132</v>
       </c>
-      <c r="C64" s="29" t="s">
+      <c r="C64" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D64" s="29">
+      <c r="D64" s="28">
         <v>1.47</v>
       </c>
-      <c r="E64" s="29" t="s">
+      <c r="E64" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F64" s="30" t="s">
+      <c r="F64" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G64" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="55"/>
-      <c r="B65" s="28">
+      <c r="G64" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="83"/>
+      <c r="B65" s="27">
         <v>133</v>
       </c>
-      <c r="C65" s="39" t="s">
+      <c r="C65" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="D65" s="29">
+      <c r="D65" s="28">
         <v>1.96</v>
       </c>
-      <c r="E65" s="29"/>
-      <c r="F65" s="30"/>
-      <c r="G65" s="30"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="55"/>
-      <c r="B66" s="28">
+      <c r="E65" s="28"/>
+      <c r="F65" s="29"/>
+      <c r="G65" s="29"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="83"/>
+      <c r="B66" s="27">
         <v>134</v>
       </c>
-      <c r="D66" s="29"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="30"/>
-      <c r="G66" s="30"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="55"/>
-      <c r="B67" s="28">
+      <c r="D66" s="28"/>
+      <c r="E66" s="28"/>
+      <c r="F66" s="29"/>
+      <c r="G66" s="29"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="83"/>
+      <c r="B67" s="27">
         <v>135</v>
       </c>
-      <c r="C67" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D67" s="29">
+      <c r="C67" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D67" s="28">
         <v>2.23</v>
       </c>
-      <c r="E67" s="29"/>
-      <c r="F67" s="30" t="s">
+      <c r="E67" s="28"/>
+      <c r="F67" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G67" s="39"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="55"/>
-      <c r="B68" s="28">
+      <c r="G67" s="38"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="83"/>
+      <c r="B68" s="27">
         <v>136</v>
       </c>
-      <c r="D68" s="29"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="30"/>
-      <c r="G68" s="30"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="55"/>
-      <c r="B69" s="28">
+      <c r="D68" s="28"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="29"/>
+      <c r="G68" s="29"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="83"/>
+      <c r="B69" s="27">
         <v>137</v>
       </c>
-      <c r="C69" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D69" s="29">
+      <c r="C69" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D69" s="28">
         <v>2.09</v>
       </c>
-      <c r="E69" s="29" t="s">
+      <c r="E69" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F69" s="30" t="s">
+      <c r="F69" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G69" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="55"/>
-      <c r="B70" s="28">
+      <c r="G69" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="83"/>
+      <c r="B70" s="27">
         <v>138</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="C70" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D70" s="29">
+      <c r="D70" s="28">
         <v>1.3</v>
       </c>
-      <c r="E70" s="29"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="55"/>
-      <c r="B71" s="28">
+      <c r="E70" s="28"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="83"/>
+      <c r="B71" s="27">
         <v>139</v>
       </c>
-      <c r="C71" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D71" s="29">
+      <c r="C71" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D71" s="28">
         <v>2.09</v>
       </c>
-      <c r="E71" s="29"/>
-      <c r="F71" s="30" t="s">
+      <c r="E71" s="28"/>
+      <c r="F71" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G71" s="39"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="55"/>
-      <c r="B72" s="28">
+      <c r="G71" s="38"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="83"/>
+      <c r="B72" s="27">
         <v>140</v>
       </c>
-      <c r="D72" s="29"/>
-      <c r="E72" s="29"/>
-      <c r="F72" s="30"/>
-      <c r="G72" s="30"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="55"/>
-      <c r="B73" s="28">
+      <c r="D72" s="28"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="29"/>
+      <c r="G72" s="29"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="83"/>
+      <c r="B73" s="27">
         <v>141</v>
       </c>
-      <c r="D73" s="29"/>
-      <c r="E73" s="29"/>
-      <c r="F73" s="30"/>
-      <c r="G73" s="30"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="55"/>
-      <c r="B74" s="28">
+      <c r="D73" s="28"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="29"/>
+      <c r="G73" s="29"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="83"/>
+      <c r="B74" s="27">
         <v>142</v>
       </c>
-      <c r="D74" s="29"/>
-      <c r="E74" s="29"/>
-      <c r="F74" s="30"/>
-      <c r="G74" s="30"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="55"/>
-      <c r="B75" s="28">
+      <c r="D74" s="28"/>
+      <c r="E74" s="28"/>
+      <c r="F74" s="29"/>
+      <c r="G74" s="29"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="83"/>
+      <c r="B75" s="27">
         <v>143</v>
       </c>
-      <c r="C75" s="39" t="s">
+      <c r="C75" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="D75" s="29">
+      <c r="D75" s="28">
         <v>1.84</v>
       </c>
-      <c r="E75" s="29"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="55"/>
-      <c r="B76" s="28">
+      <c r="E75" s="28"/>
+      <c r="F75" s="29"/>
+      <c r="G75" s="29"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="83"/>
+      <c r="B76" s="27">
         <v>144</v>
       </c>
-      <c r="D76" s="29"/>
-      <c r="E76" s="29"/>
-      <c r="F76" s="30"/>
-      <c r="G76" s="30"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="55"/>
-      <c r="B77" s="28">
+      <c r="D76" s="28"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="29"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="83"/>
+      <c r="B77" s="27">
         <v>145</v>
       </c>
-      <c r="C77" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D77" s="29">
+      <c r="C77" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D77" s="28">
         <v>2.0299999999999998</v>
       </c>
-      <c r="E77" s="29" t="s">
+      <c r="E77" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F77" s="30" t="s">
+      <c r="F77" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G77" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="55"/>
-      <c r="B78" s="28">
+      <c r="G77" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="83"/>
+      <c r="B78" s="27">
         <v>146</v>
       </c>
-      <c r="C78" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D78" s="29">
+      <c r="C78" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D78" s="28">
         <v>2.09</v>
       </c>
-      <c r="E78" s="29" t="s">
+      <c r="E78" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F78" s="30" t="s">
+      <c r="F78" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G78" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="55"/>
-      <c r="B79" s="28">
+      <c r="G78" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="83"/>
+      <c r="B79" s="27">
         <v>147</v>
       </c>
-      <c r="D79" s="29"/>
-      <c r="E79" s="29"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="55"/>
-      <c r="B80" s="28">
+      <c r="D79" s="28"/>
+      <c r="E79" s="28"/>
+      <c r="F79" s="29"/>
+      <c r="G79" s="29"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="83"/>
+      <c r="B80" s="27">
         <v>148</v>
       </c>
-      <c r="C80" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D80" s="29">
+      <c r="C80" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D80" s="28">
         <v>2.11</v>
       </c>
-      <c r="E80" s="29" t="s">
+      <c r="E80" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F80" s="30" t="s">
+      <c r="F80" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G80" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="55"/>
-      <c r="B81" s="28">
+      <c r="G80" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="83"/>
+      <c r="B81" s="27">
         <v>149</v>
       </c>
-      <c r="C81" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D81" s="29">
+      <c r="C81" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D81" s="28">
         <v>1.93</v>
       </c>
-      <c r="E81" s="29"/>
-      <c r="F81" s="30" t="s">
+      <c r="E81" s="28"/>
+      <c r="F81" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G81" s="39"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="55"/>
-      <c r="B82" s="28">
+      <c r="G81" s="38"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="83"/>
+      <c r="B82" s="27">
         <v>150</v>
       </c>
-      <c r="D82" s="29"/>
-      <c r="E82" s="29"/>
-      <c r="F82" s="30"/>
-      <c r="G82" s="30"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="55"/>
-      <c r="B83" s="28">
+      <c r="D82" s="28"/>
+      <c r="E82" s="28"/>
+      <c r="F82" s="29"/>
+      <c r="G82" s="29"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="83"/>
+      <c r="B83" s="27">
         <v>151</v>
       </c>
-      <c r="C83" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D83" s="29">
+      <c r="C83" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D83" s="28">
         <v>1.96</v>
       </c>
-      <c r="E83" s="29"/>
-      <c r="F83" s="29" t="s">
+      <c r="E83" s="28"/>
+      <c r="F83" s="28" t="s">
         <v>329</v>
       </c>
-      <c r="G83" s="39"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="55"/>
-      <c r="B84" s="28">
+      <c r="G83" s="38"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="83"/>
+      <c r="B84" s="27">
         <v>152</v>
       </c>
-      <c r="C84" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D84" s="29">
+      <c r="C84" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D84" s="28">
         <v>1.98</v>
       </c>
-      <c r="E84" s="29"/>
-      <c r="F84" s="29" t="s">
+      <c r="E84" s="28"/>
+      <c r="F84" s="28" t="s">
         <v>329</v>
       </c>
-      <c r="G84" s="39"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="55"/>
-      <c r="B85" s="28">
+      <c r="G84" s="38"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="83"/>
+      <c r="B85" s="27">
         <v>153</v>
       </c>
-      <c r="C85" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D85" s="29">
+      <c r="C85" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D85" s="28">
         <v>1.98</v>
       </c>
-      <c r="E85" s="29"/>
-      <c r="F85" s="29" t="s">
+      <c r="E85" s="28"/>
+      <c r="F85" s="28" t="s">
         <v>329</v>
       </c>
-      <c r="G85" s="39"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="55"/>
-      <c r="B86" s="28">
+      <c r="G85" s="38"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="83"/>
+      <c r="B86" s="27">
         <v>154</v>
       </c>
-      <c r="C86" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D86" s="29">
+      <c r="C86" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D86" s="28">
         <v>2.06</v>
       </c>
-      <c r="E86" s="29" t="s">
+      <c r="E86" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F86" s="30" t="s">
+      <c r="F86" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G86" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="55"/>
-      <c r="B87" s="28">
+      <c r="G86" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="83"/>
+      <c r="B87" s="27">
         <v>155</v>
       </c>
-      <c r="C87" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D87" s="29">
+      <c r="C87" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D87" s="28">
         <v>1.76</v>
       </c>
-      <c r="E87" s="29"/>
-      <c r="F87" s="29" t="s">
+      <c r="E87" s="28"/>
+      <c r="F87" s="28" t="s">
         <v>329</v>
       </c>
-      <c r="G87" s="39"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="55"/>
-      <c r="B88" s="28">
+      <c r="G87" s="38"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="83"/>
+      <c r="B88" s="27">
         <v>156</v>
       </c>
-      <c r="C88" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D88" s="29">
+      <c r="C88" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D88" s="28">
         <v>2</v>
       </c>
-      <c r="E88" s="29" t="s">
+      <c r="E88" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F88" s="30" t="s">
+      <c r="F88" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G88" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="55"/>
-      <c r="B89" s="28">
+      <c r="G88" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="83"/>
+      <c r="B89" s="27">
         <v>157</v>
       </c>
-      <c r="C89" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D89" s="29">
+      <c r="C89" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D89" s="28">
         <v>1.72</v>
       </c>
-      <c r="E89" s="29" t="s">
+      <c r="E89" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F89" s="30" t="s">
+      <c r="F89" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G89" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="55"/>
-      <c r="B90" s="28">
+      <c r="G89" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="83"/>
+      <c r="B90" s="27">
         <v>158</v>
       </c>
-      <c r="C90" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D90" s="29">
+      <c r="C90" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D90" s="28">
         <v>2.15</v>
       </c>
-      <c r="E90" s="29" t="s">
+      <c r="E90" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F90" s="30" t="s">
+      <c r="F90" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G90" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="55"/>
-      <c r="B91" s="28">
+      <c r="G90" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="83"/>
+      <c r="B91" s="27">
         <v>159</v>
       </c>
-      <c r="C91" s="29" t="s">
+      <c r="C91" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D91" s="29">
+      <c r="D91" s="28">
         <v>1.3</v>
       </c>
-      <c r="E91" s="29"/>
-      <c r="F91" s="30"/>
-      <c r="G91" s="30"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="55"/>
-      <c r="B92" s="28">
+      <c r="E91" s="28"/>
+      <c r="F91" s="29"/>
+      <c r="G91" s="29"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="83"/>
+      <c r="B92" s="27">
         <v>160</v>
       </c>
-      <c r="D92" s="29"/>
-      <c r="E92" s="29"/>
-      <c r="F92" s="30"/>
-      <c r="G92" s="30"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="55"/>
-      <c r="B93" s="28">
+      <c r="D92" s="28"/>
+      <c r="E92" s="28"/>
+      <c r="F92" s="29"/>
+      <c r="G92" s="29"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="83"/>
+      <c r="B93" s="27">
         <v>161</v>
       </c>
-      <c r="C93" s="29" t="s">
+      <c r="C93" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D93" s="29">
+      <c r="D93" s="28">
         <v>1.3</v>
       </c>
-      <c r="E93" s="29"/>
-      <c r="F93" s="30"/>
-      <c r="G93" s="30"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="55"/>
-      <c r="B94" s="28">
+      <c r="E93" s="28"/>
+      <c r="F93" s="29"/>
+      <c r="G93" s="29"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="83"/>
+      <c r="B94" s="27">
         <v>162</v>
       </c>
-      <c r="C94" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D94" s="29">
+      <c r="C94" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D94" s="28">
         <v>2.02</v>
       </c>
-      <c r="E94" s="29" t="s">
+      <c r="E94" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F94" s="30" t="s">
+      <c r="F94" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G94" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="55"/>
-      <c r="B95" s="28">
+      <c r="G94" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="83"/>
+      <c r="B95" s="27">
         <v>163</v>
       </c>
-      <c r="C95" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D95" s="29">
+      <c r="C95" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D95" s="28">
         <v>1.83</v>
       </c>
-      <c r="E95" s="29"/>
-      <c r="F95" s="30" t="s">
+      <c r="E95" s="28"/>
+      <c r="F95" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G95" s="39"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="55"/>
-      <c r="B96" s="28">
+      <c r="G95" s="38"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="83"/>
+      <c r="B96" s="27">
         <v>164</v>
       </c>
-      <c r="D96" s="29"/>
-      <c r="E96" s="29"/>
-      <c r="F96" s="30"/>
-      <c r="G96" s="30"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="55"/>
-      <c r="B97" s="28">
+      <c r="D96" s="28"/>
+      <c r="E96" s="28"/>
+      <c r="F96" s="29"/>
+      <c r="G96" s="29"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" s="83"/>
+      <c r="B97" s="27">
         <v>166</v>
       </c>
-      <c r="D97" s="29"/>
-      <c r="E97" s="29"/>
-      <c r="F97" s="30"/>
-      <c r="G97" s="30"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="55"/>
-      <c r="B98" s="28">
+      <c r="D97" s="28"/>
+      <c r="E97" s="28"/>
+      <c r="F97" s="29"/>
+      <c r="G97" s="29"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="83"/>
+      <c r="B98" s="27">
         <v>167</v>
       </c>
-      <c r="C98" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D98" s="29">
+      <c r="C98" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D98" s="28">
         <v>1.93</v>
       </c>
-      <c r="E98" s="29"/>
-      <c r="F98" s="30" t="s">
+      <c r="E98" s="28"/>
+      <c r="F98" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G98" s="39"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="55"/>
-      <c r="B99" s="28">
+      <c r="G98" s="38"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" s="83"/>
+      <c r="B99" s="27">
         <v>168</v>
       </c>
-      <c r="C99" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D99" s="29">
+      <c r="C99" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D99" s="28">
         <v>1.94</v>
       </c>
-      <c r="E99" s="29"/>
-      <c r="F99" s="30" t="s">
+      <c r="E99" s="28"/>
+      <c r="F99" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G99" s="39"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="55"/>
-      <c r="B100" s="28">
+      <c r="G99" s="38"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="83"/>
+      <c r="B100" s="27">
         <v>169</v>
       </c>
-      <c r="D100" s="29"/>
-      <c r="E100" s="29"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="55"/>
-      <c r="B101" s="28">
+      <c r="D100" s="28"/>
+      <c r="E100" s="28"/>
+      <c r="F100" s="29"/>
+      <c r="G100" s="29"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="83"/>
+      <c r="B101" s="27">
         <v>170</v>
       </c>
-      <c r="C101" s="29" t="s">
+      <c r="C101" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D101" s="29"/>
-      <c r="E101" s="29"/>
-      <c r="F101" s="30"/>
-      <c r="G101" s="30"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="55"/>
-      <c r="B102" s="28">
+      <c r="D101" s="28"/>
+      <c r="E101" s="28"/>
+      <c r="F101" s="29"/>
+      <c r="G101" s="29"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="83"/>
+      <c r="B102" s="27">
         <v>171</v>
       </c>
-      <c r="C102" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D102" s="29">
+      <c r="C102" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D102" s="28">
         <v>2.09</v>
       </c>
-      <c r="E102" s="29"/>
-      <c r="F102" s="30" t="s">
+      <c r="E102" s="28"/>
+      <c r="F102" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G102" s="39"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="55"/>
-      <c r="B103" s="28">
+      <c r="G102" s="38"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="83"/>
+      <c r="B103" s="27">
         <v>172</v>
       </c>
-      <c r="C103" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D103" s="29">
+      <c r="C103" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D103" s="28">
         <v>2.08</v>
       </c>
-      <c r="E103" s="29" t="s">
+      <c r="E103" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F103" s="30" t="s">
+      <c r="F103" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G103" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="55"/>
-      <c r="B104" s="28">
+      <c r="G103" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="83"/>
+      <c r="B104" s="27">
         <v>173</v>
       </c>
-      <c r="C104" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D104" s="29">
+      <c r="C104" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D104" s="28">
         <v>1.95</v>
       </c>
-      <c r="E104" s="29"/>
-      <c r="F104" s="30" t="s">
+      <c r="E104" s="28"/>
+      <c r="F104" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G104" s="39"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="55"/>
-      <c r="B105" s="28">
+      <c r="G104" s="38"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="83"/>
+      <c r="B105" s="27">
         <v>174</v>
       </c>
-      <c r="C105" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D105" s="29">
+      <c r="C105" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D105" s="28">
         <v>1.93</v>
       </c>
-      <c r="E105" s="29"/>
-      <c r="F105" s="30" t="s">
+      <c r="E105" s="28"/>
+      <c r="F105" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G105" s="39"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="55"/>
-      <c r="B106" s="28">
+      <c r="G105" s="38"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106" s="83"/>
+      <c r="B106" s="27">
         <v>175</v>
       </c>
-      <c r="D106" s="29"/>
-      <c r="E106" s="29"/>
-      <c r="F106" s="30"/>
-      <c r="G106" s="30"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="55"/>
-      <c r="B107" s="28">
+      <c r="D106" s="28"/>
+      <c r="E106" s="28"/>
+      <c r="F106" s="29"/>
+      <c r="G106" s="29"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" s="83"/>
+      <c r="B107" s="27">
         <v>176</v>
       </c>
-      <c r="C107" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D107" s="29">
+      <c r="C107" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D107" s="28">
         <v>2.06</v>
       </c>
-      <c r="E107" s="29" t="s">
+      <c r="E107" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F107" s="30" t="s">
+      <c r="F107" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G107" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="55"/>
-      <c r="B108" s="28">
+      <c r="G107" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="83"/>
+      <c r="B108" s="27">
         <v>177</v>
       </c>
-      <c r="D108" s="29"/>
-      <c r="E108" s="29"/>
-      <c r="F108" s="30"/>
-      <c r="G108" s="30"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="55"/>
-      <c r="B109" s="28">
+      <c r="D108" s="28"/>
+      <c r="E108" s="28"/>
+      <c r="F108" s="29"/>
+      <c r="G108" s="29"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" s="83"/>
+      <c r="B109" s="27">
         <v>178</v>
       </c>
-      <c r="C109" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D109" s="29">
+      <c r="C109" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D109" s="28">
         <v>2.0499999999999998</v>
       </c>
-      <c r="E109" s="29"/>
-      <c r="F109" s="30" t="s">
+      <c r="E109" s="28"/>
+      <c r="F109" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G109" s="39"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="55"/>
-      <c r="B110" s="28">
+      <c r="G109" s="38"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" s="83"/>
+      <c r="B110" s="27">
         <v>179</v>
       </c>
-      <c r="C110" s="29" t="s">
+      <c r="C110" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D110" s="29"/>
-      <c r="E110" s="29"/>
-      <c r="F110" s="30"/>
-      <c r="G110" s="30"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="55"/>
-      <c r="B111" s="28">
+      <c r="D110" s="28"/>
+      <c r="E110" s="28"/>
+      <c r="F110" s="29"/>
+      <c r="G110" s="29"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" s="83"/>
+      <c r="B111" s="27">
         <v>180</v>
       </c>
-      <c r="C111" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D111" s="29">
+      <c r="C111" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D111" s="28">
         <v>1.81</v>
       </c>
-      <c r="E111" s="29"/>
-      <c r="F111" s="30" t="s">
+      <c r="E111" s="28"/>
+      <c r="F111" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G111" s="39"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="55"/>
-      <c r="B112" s="28">
+      <c r="G111" s="38"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" s="83"/>
+      <c r="B112" s="27">
         <v>181</v>
       </c>
-      <c r="C112" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D112" s="29">
+      <c r="C112" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D112" s="28">
         <v>2.0699999999999998</v>
       </c>
-      <c r="E112" s="29" t="s">
+      <c r="E112" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F112" s="30" t="s">
+      <c r="F112" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G112" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="55"/>
-      <c r="B113" s="28">
+      <c r="G112" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" s="83"/>
+      <c r="B113" s="27">
         <v>182</v>
       </c>
-      <c r="C113" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D113" s="29">
+      <c r="C113" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D113" s="28">
         <v>2.0699999999999998</v>
       </c>
-      <c r="E113" s="29"/>
-      <c r="F113" s="30" t="s">
+      <c r="E113" s="28"/>
+      <c r="F113" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G113" s="39"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="55"/>
-      <c r="B114" s="28">
+      <c r="G113" s="38"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" s="83"/>
+      <c r="B114" s="27">
         <v>183</v>
       </c>
-      <c r="C114" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D114" s="29">
+      <c r="C114" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D114" s="28">
         <v>2</v>
       </c>
-      <c r="E114" s="29" t="s">
+      <c r="E114" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F114" s="30" t="s">
+      <c r="F114" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G114" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="55"/>
-      <c r="B115" s="28">
+      <c r="G114" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" s="83"/>
+      <c r="B115" s="27">
         <v>184</v>
       </c>
-      <c r="D115" s="29"/>
-      <c r="E115" s="29"/>
-      <c r="F115" s="30"/>
-      <c r="G115" s="30"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="55"/>
-      <c r="B116" s="28">
+      <c r="D115" s="28"/>
+      <c r="E115" s="28"/>
+      <c r="F115" s="29"/>
+      <c r="G115" s="29"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" s="83"/>
+      <c r="B116" s="27">
         <v>185</v>
       </c>
-      <c r="D116" s="29"/>
-      <c r="E116" s="29"/>
-      <c r="F116" s="30"/>
-      <c r="G116" s="30"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="55"/>
-      <c r="B117" s="28">
+      <c r="D116" s="28"/>
+      <c r="E116" s="28"/>
+      <c r="F116" s="29"/>
+      <c r="G116" s="29"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" s="83"/>
+      <c r="B117" s="27">
         <v>186</v>
       </c>
-      <c r="C117" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D117" s="29">
+      <c r="C117" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D117" s="28">
         <v>1.86</v>
       </c>
-      <c r="E117" s="29"/>
-      <c r="F117" s="30" t="s">
+      <c r="E117" s="28"/>
+      <c r="F117" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G117" s="39"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="55"/>
-      <c r="B118" s="28">
+      <c r="G117" s="38"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="83"/>
+      <c r="B118" s="27">
         <v>187</v>
       </c>
-      <c r="C118" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D118" s="29">
+      <c r="C118" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D118" s="28">
         <v>2.04</v>
       </c>
-      <c r="E118" s="29" t="s">
+      <c r="E118" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F118" s="30" t="s">
+      <c r="F118" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G118" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="55"/>
-      <c r="B119" s="28">
+      <c r="G118" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" s="83"/>
+      <c r="B119" s="27">
         <v>188</v>
       </c>
-      <c r="C119" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D119" s="29">
+      <c r="C119" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D119" s="28">
         <v>2.21</v>
       </c>
-      <c r="E119" s="29" t="s">
+      <c r="E119" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F119" s="30" t="s">
+      <c r="F119" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G119" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="55"/>
-      <c r="B120" s="28">
+      <c r="G119" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" s="83"/>
+      <c r="B120" s="27">
         <v>189</v>
       </c>
-      <c r="C120" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D120" s="29">
+      <c r="C120" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D120" s="28">
         <v>1.79</v>
       </c>
-      <c r="E120" s="29"/>
-      <c r="F120" s="30" t="s">
+      <c r="E120" s="28"/>
+      <c r="F120" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G120" s="39"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="55"/>
-      <c r="B121" s="28">
+      <c r="G120" s="38"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" s="83"/>
+      <c r="B121" s="27">
         <v>190</v>
       </c>
-      <c r="C121" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D121" s="29">
+      <c r="C121" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D121" s="28">
         <v>2.0299999999999998</v>
       </c>
-      <c r="E121" s="29" t="s">
+      <c r="E121" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F121" s="30" t="s">
+      <c r="F121" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G121" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="55"/>
-      <c r="B122" s="28">
+      <c r="G121" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="83"/>
+      <c r="B122" s="27">
         <v>191</v>
       </c>
-      <c r="D122" s="29"/>
-      <c r="E122" s="29"/>
-      <c r="F122" s="30"/>
-      <c r="G122" s="30"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="55"/>
-      <c r="B123" s="28">
+      <c r="D122" s="28"/>
+      <c r="E122" s="28"/>
+      <c r="F122" s="29"/>
+      <c r="G122" s="29"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" s="83"/>
+      <c r="B123" s="27">
         <v>192</v>
       </c>
-      <c r="C123" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D123" s="29">
+      <c r="C123" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D123" s="28">
         <v>1.99</v>
       </c>
-      <c r="E123" s="29"/>
-      <c r="F123" s="30" t="s">
+      <c r="E123" s="28"/>
+      <c r="F123" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G123" s="39"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="55"/>
-      <c r="B124" s="28">
+      <c r="G123" s="38"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" s="83"/>
+      <c r="B124" s="27">
         <v>193</v>
       </c>
-      <c r="D124" s="29"/>
-      <c r="E124" s="29"/>
-      <c r="F124" s="30"/>
-      <c r="G124" s="30"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="55"/>
-      <c r="B125" s="28">
+      <c r="D124" s="28"/>
+      <c r="E124" s="28"/>
+      <c r="F124" s="29"/>
+      <c r="G124" s="29"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="83"/>
+      <c r="B125" s="27">
         <v>194</v>
       </c>
-      <c r="C125" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D125" s="29">
+      <c r="C125" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D125" s="28">
         <v>2.0299999999999998</v>
       </c>
-      <c r="E125" s="29" t="s">
+      <c r="E125" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F125" s="30" t="s">
+      <c r="F125" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G125" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="55"/>
-      <c r="B126" s="28">
+      <c r="G125" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" s="83"/>
+      <c r="B126" s="27">
         <v>195</v>
       </c>
-      <c r="C126" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D126" s="29">
+      <c r="C126" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D126" s="28">
         <v>2.15</v>
       </c>
-      <c r="E126" s="29"/>
-      <c r="F126" s="30" t="s">
+      <c r="E126" s="28"/>
+      <c r="F126" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G126" s="39"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="55"/>
-      <c r="B127" s="28">
+      <c r="G126" s="38"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="83"/>
+      <c r="B127" s="27">
         <v>196</v>
       </c>
-      <c r="C127" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D127" s="29">
+      <c r="C127" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D127" s="28">
         <v>2.0299999999999998</v>
       </c>
-      <c r="E127" s="29"/>
-      <c r="F127" s="30" t="s">
+      <c r="E127" s="28"/>
+      <c r="F127" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G127" s="39"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="56"/>
-      <c r="B128" s="37">
+      <c r="G127" s="38"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="84"/>
+      <c r="B128" s="36">
         <v>197</v>
       </c>
-      <c r="C128" s="40"/>
-      <c r="D128" s="36"/>
-      <c r="E128" s="36"/>
-      <c r="F128" s="43"/>
-      <c r="G128" s="43"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129" s="57" t="s">
+      <c r="C128" s="39"/>
+      <c r="D128" s="35"/>
+      <c r="E128" s="35"/>
+      <c r="F128" s="42"/>
+      <c r="G128" s="42"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="85" t="s">
         <v>306</v>
       </c>
-      <c r="B129" s="32">
+      <c r="B129" s="31">
         <v>198</v>
       </c>
-      <c r="C129" s="35" t="s">
+      <c r="C129" s="34" t="s">
         <v>319</v>
       </c>
-      <c r="D129" s="35"/>
-      <c r="E129" s="35"/>
-      <c r="F129" s="44"/>
-      <c r="G129" s="44"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130" s="55"/>
-      <c r="B130" s="28">
+      <c r="D129" s="34"/>
+      <c r="E129" s="34"/>
+      <c r="F129" s="43"/>
+      <c r="G129" s="43"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" s="83"/>
+      <c r="B130" s="27">
         <v>199</v>
       </c>
-      <c r="C130" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D130" s="29">
+      <c r="C130" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D130" s="28">
         <v>1.93</v>
       </c>
-      <c r="E130" s="29"/>
-      <c r="F130" s="30" t="s">
+      <c r="E130" s="28"/>
+      <c r="F130" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G130" s="39"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="55"/>
-      <c r="B131" s="28">
+      <c r="G130" s="38"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" s="83"/>
+      <c r="B131" s="27">
         <v>200</v>
       </c>
-      <c r="C131" s="39" t="s">
+      <c r="C131" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="D131" s="29">
+      <c r="D131" s="28">
         <v>1.72</v>
       </c>
-      <c r="E131" s="29"/>
-      <c r="F131" s="30"/>
-      <c r="G131" s="30"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132" s="55"/>
-      <c r="B132" s="28">
+      <c r="E131" s="28"/>
+      <c r="F131" s="29"/>
+      <c r="G131" s="29"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" s="83"/>
+      <c r="B132" s="27">
         <v>201</v>
       </c>
-      <c r="C132" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D132" s="29">
+      <c r="C132" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D132" s="28">
         <v>1.82</v>
       </c>
-      <c r="E132" s="29"/>
-      <c r="F132" s="30" t="s">
+      <c r="E132" s="28"/>
+      <c r="F132" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G132" s="39"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="55"/>
-      <c r="B133" s="28">
+      <c r="G132" s="38"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" s="83"/>
+      <c r="B133" s="27">
         <v>202</v>
       </c>
-      <c r="C133" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D133" s="29">
+      <c r="C133" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D133" s="28">
         <v>2.1</v>
       </c>
-      <c r="E133" s="29" t="s">
+      <c r="E133" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F133" s="30" t="s">
+      <c r="F133" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G133" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="55"/>
-      <c r="B134" s="28">
+      <c r="G133" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" s="83"/>
+      <c r="B134" s="27">
         <v>203</v>
       </c>
-      <c r="C134" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D134" s="29">
+      <c r="C134" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D134" s="28">
         <v>1.95</v>
       </c>
-      <c r="E134" s="29"/>
-      <c r="F134" s="30" t="s">
+      <c r="E134" s="28"/>
+      <c r="F134" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G134" s="39"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="55"/>
-      <c r="B135" s="28">
+      <c r="G134" s="38"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" s="83"/>
+      <c r="B135" s="27">
         <v>204</v>
       </c>
-      <c r="C135" s="29" t="s">
+      <c r="C135" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D135" s="29">
+      <c r="D135" s="28">
         <v>1.42</v>
       </c>
-      <c r="E135" s="29"/>
-      <c r="F135" s="30"/>
-      <c r="G135" s="30"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="55"/>
-      <c r="B136" s="28">
+      <c r="E135" s="28"/>
+      <c r="F135" s="29"/>
+      <c r="G135" s="29"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" s="83"/>
+      <c r="B136" s="27">
         <v>205</v>
       </c>
-      <c r="C136" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D136" s="29">
+      <c r="C136" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D136" s="28">
         <v>2.0699999999999998</v>
       </c>
-      <c r="E136" s="29" t="s">
+      <c r="E136" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F136" s="30" t="s">
+      <c r="F136" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G136" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="55"/>
-      <c r="B137" s="28">
+      <c r="G136" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" s="83"/>
+      <c r="B137" s="27">
         <v>206</v>
       </c>
-      <c r="C137" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D137" s="29">
+      <c r="C137" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D137" s="28">
         <v>2.0499999999999998</v>
       </c>
-      <c r="E137" s="29"/>
-      <c r="F137" s="30" t="s">
+      <c r="E137" s="28"/>
+      <c r="F137" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G137" s="39"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="55"/>
-      <c r="B138" s="28">
+      <c r="G137" s="38"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" s="83"/>
+      <c r="B138" s="27">
         <v>207</v>
       </c>
-      <c r="C138" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D138" s="29">
+      <c r="C138" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D138" s="28">
         <v>2.04</v>
       </c>
-      <c r="E138" s="29"/>
-      <c r="F138" s="30" t="s">
+      <c r="E138" s="28"/>
+      <c r="F138" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G138" s="39"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" s="55"/>
-      <c r="B139" s="28">
+      <c r="G138" s="38"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" s="83"/>
+      <c r="B139" s="27">
         <v>208</v>
       </c>
-      <c r="C139" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D139" s="29">
+      <c r="C139" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D139" s="28">
         <v>1.9</v>
       </c>
-      <c r="E139" s="29"/>
-      <c r="F139" s="30" t="s">
+      <c r="E139" s="28"/>
+      <c r="F139" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G139" s="39"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140" s="55"/>
-      <c r="B140" s="28">
+      <c r="G139" s="38"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" s="83"/>
+      <c r="B140" s="27">
         <v>209</v>
       </c>
-      <c r="C140" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D140" s="29">
+      <c r="C140" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D140" s="28">
         <v>1.98</v>
       </c>
-      <c r="E140" s="29"/>
-      <c r="F140" s="30" t="s">
+      <c r="E140" s="28"/>
+      <c r="F140" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G140" s="39"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" s="55"/>
-      <c r="B141" s="28">
+      <c r="G140" s="38"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" s="83"/>
+      <c r="B141" s="27">
         <v>210</v>
       </c>
-      <c r="C141" s="29" t="s">
+      <c r="C141" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D141" s="29">
+      <c r="D141" s="28">
         <v>1.31</v>
       </c>
-      <c r="E141" s="29"/>
-      <c r="F141" s="30"/>
-      <c r="G141" s="30"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142" s="55"/>
-      <c r="B142" s="28">
+      <c r="E141" s="28"/>
+      <c r="F141" s="29"/>
+      <c r="G141" s="29"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142" s="83"/>
+      <c r="B142" s="27">
         <v>211</v>
       </c>
-      <c r="C142" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D142" s="29">
+      <c r="C142" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D142" s="28">
         <v>2.1800000000000002</v>
       </c>
-      <c r="E142" s="29" t="s">
+      <c r="E142" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F142" s="30" t="s">
+      <c r="F142" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G142" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" s="55"/>
-      <c r="B143" s="28">
+      <c r="G142" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" s="83"/>
+      <c r="B143" s="27">
         <v>212</v>
       </c>
-      <c r="D143" s="29"/>
-      <c r="E143" s="29"/>
-      <c r="F143" s="30"/>
-      <c r="G143" s="30"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" s="55"/>
-      <c r="B144" s="28">
+      <c r="D143" s="28"/>
+      <c r="E143" s="28"/>
+      <c r="F143" s="29"/>
+      <c r="G143" s="29"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144" s="83"/>
+      <c r="B144" s="27">
         <v>213</v>
       </c>
-      <c r="C144" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D144" s="29">
+      <c r="C144" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D144" s="28">
         <v>2.09</v>
       </c>
-      <c r="E144" s="29" t="s">
+      <c r="E144" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F144" s="30" t="s">
+      <c r="F144" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G144" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="55"/>
-      <c r="B145" s="28">
+      <c r="G144" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A145" s="83"/>
+      <c r="B145" s="27">
         <v>214</v>
       </c>
-      <c r="C145" s="29" t="s">
+      <c r="C145" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D145" s="29">
+      <c r="D145" s="28">
         <v>1.56</v>
       </c>
-      <c r="E145" s="29"/>
-      <c r="F145" s="30"/>
-      <c r="G145" s="30"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" s="55"/>
-      <c r="B146" s="28">
+      <c r="E145" s="28"/>
+      <c r="F145" s="29"/>
+      <c r="G145" s="29"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A146" s="83"/>
+      <c r="B146" s="27">
         <v>215</v>
       </c>
-      <c r="C146" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D146" s="29">
+      <c r="C146" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D146" s="28">
         <v>2.0499999999999998</v>
       </c>
-      <c r="E146" s="29" t="s">
+      <c r="E146" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F146" s="30" t="s">
+      <c r="F146" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G146" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" s="55"/>
-      <c r="B147" s="28">
+      <c r="G146" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147" s="83"/>
+      <c r="B147" s="27">
         <v>216</v>
       </c>
-      <c r="D147" s="29"/>
-      <c r="E147" s="29"/>
-      <c r="F147" s="30"/>
-      <c r="G147" s="30"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" s="55"/>
-      <c r="B148" s="28">
+      <c r="D147" s="28"/>
+      <c r="E147" s="28"/>
+      <c r="F147" s="29"/>
+      <c r="G147" s="29"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A148" s="83"/>
+      <c r="B148" s="27">
         <v>217</v>
       </c>
-      <c r="C148" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D148" s="29">
+      <c r="C148" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D148" s="28">
         <v>2.21</v>
       </c>
-      <c r="E148" s="29" t="s">
+      <c r="E148" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F148" s="30" t="s">
+      <c r="F148" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G148" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" s="55"/>
-      <c r="B149" s="28">
+      <c r="G148" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149" s="83"/>
+      <c r="B149" s="27">
         <v>218</v>
       </c>
-      <c r="C149" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D149" s="29">
+      <c r="C149" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D149" s="28">
         <v>1.9</v>
       </c>
-      <c r="E149" s="29" t="s">
+      <c r="E149" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F149" s="30" t="s">
+      <c r="F149" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G149" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150" s="55"/>
-      <c r="B150" s="28">
+      <c r="G149" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150" s="83"/>
+      <c r="B150" s="27">
         <v>219</v>
       </c>
-      <c r="C150" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D150" s="29">
+      <c r="C150" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D150" s="28">
         <v>1.97</v>
       </c>
-      <c r="E150" s="29" t="s">
+      <c r="E150" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F150" s="30" t="s">
+      <c r="F150" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G150" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" s="55"/>
-      <c r="B151" s="28">
+      <c r="G150" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151" s="83"/>
+      <c r="B151" s="27">
         <v>220</v>
       </c>
-      <c r="C151" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D151" s="29">
+      <c r="C151" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D151" s="28">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E151" s="29" t="s">
+      <c r="E151" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F151" s="30" t="s">
+      <c r="F151" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G151" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A152" s="55"/>
-      <c r="B152" s="28">
+      <c r="G151" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152" s="83"/>
+      <c r="B152" s="27">
         <v>221</v>
       </c>
-      <c r="C152" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D152" s="29">
+      <c r="C152" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D152" s="28">
         <v>1.99</v>
       </c>
-      <c r="E152" s="29" t="s">
+      <c r="E152" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F152" s="30" t="s">
+      <c r="F152" s="29" t="s">
         <v>325</v>
       </c>
-      <c r="G152" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153" s="55"/>
-      <c r="B153" s="28">
+      <c r="G152" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" s="83"/>
+      <c r="B153" s="27">
         <v>222</v>
       </c>
-      <c r="C153" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D153" s="29">
+      <c r="C153" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D153" s="28">
         <v>1.98</v>
       </c>
-      <c r="E153" s="29"/>
-      <c r="F153" s="30" t="s">
+      <c r="E153" s="28"/>
+      <c r="F153" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G153" s="39"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154" s="55"/>
-      <c r="B154" s="28">
+      <c r="G153" s="38"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154" s="83"/>
+      <c r="B154" s="27">
         <v>223</v>
       </c>
-      <c r="D154" s="29"/>
-      <c r="E154" s="29"/>
-      <c r="F154" s="30"/>
-      <c r="G154" s="30"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A155" s="55"/>
-      <c r="B155" s="28">
+      <c r="D154" s="28"/>
+      <c r="E154" s="28"/>
+      <c r="F154" s="29"/>
+      <c r="G154" s="29"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" s="83"/>
+      <c r="B155" s="27">
         <v>224</v>
       </c>
-      <c r="D155" s="29"/>
-      <c r="E155" s="29"/>
-      <c r="F155" s="30"/>
-      <c r="G155" s="30"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A156" s="55"/>
-      <c r="B156" s="28">
+      <c r="D155" s="28"/>
+      <c r="E155" s="28"/>
+      <c r="F155" s="29"/>
+      <c r="G155" s="29"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" s="83"/>
+      <c r="B156" s="27">
         <v>225</v>
       </c>
-      <c r="D156" s="29"/>
-      <c r="E156" s="29"/>
-      <c r="F156" s="30"/>
-      <c r="G156" s="30"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A157" s="55"/>
-      <c r="B157" s="28">
+      <c r="D156" s="28"/>
+      <c r="E156" s="28"/>
+      <c r="F156" s="29"/>
+      <c r="G156" s="29"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" s="83"/>
+      <c r="B157" s="27">
         <v>226</v>
       </c>
-      <c r="C157" s="29" t="s">
+      <c r="C157" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D157" s="29"/>
-      <c r="E157" s="29"/>
-      <c r="F157" s="30"/>
-      <c r="G157" s="30"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A158" s="55"/>
-      <c r="B158" s="28">
+      <c r="D157" s="28"/>
+      <c r="E157" s="28"/>
+      <c r="F157" s="29"/>
+      <c r="G157" s="29"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" s="83"/>
+      <c r="B158" s="27">
         <v>227</v>
       </c>
-      <c r="D158" s="29"/>
-      <c r="E158" s="29"/>
-      <c r="F158" s="30"/>
-      <c r="G158" s="30"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A159" s="55"/>
-      <c r="B159" s="28">
+      <c r="D158" s="28"/>
+      <c r="E158" s="28"/>
+      <c r="F158" s="29"/>
+      <c r="G158" s="29"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" s="83"/>
+      <c r="B159" s="27">
         <v>228</v>
       </c>
-      <c r="C159" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D159" s="29">
+      <c r="C159" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D159" s="28">
         <v>1.78</v>
       </c>
-      <c r="E159" s="29" t="s">
+      <c r="E159" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F159" s="30" t="s">
+      <c r="F159" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G159" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A160" s="55"/>
-      <c r="B160" s="28">
+      <c r="G159" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" s="83"/>
+      <c r="B160" s="27">
         <v>229</v>
       </c>
-      <c r="D160" s="29"/>
-      <c r="E160" s="29"/>
-      <c r="F160" s="30"/>
-      <c r="G160" s="30"/>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="55"/>
-      <c r="B161" s="28">
+      <c r="D160" s="28"/>
+      <c r="E160" s="28"/>
+      <c r="F160" s="29"/>
+      <c r="G160" s="29"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" s="83"/>
+      <c r="B161" s="27">
         <v>230</v>
       </c>
-      <c r="C161" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D161" s="29">
+      <c r="C161" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D161" s="28">
         <v>1.74</v>
       </c>
-      <c r="E161" s="29" t="s">
+      <c r="E161" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F161" s="30" t="s">
+      <c r="F161" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G161" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A162" s="55"/>
-      <c r="B162" s="28">
+      <c r="G161" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" s="83"/>
+      <c r="B162" s="27">
         <v>231</v>
       </c>
-      <c r="D162" s="29"/>
-      <c r="E162" s="29"/>
-      <c r="F162" s="30"/>
-      <c r="G162" s="30"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A163" s="55"/>
-      <c r="B163" s="28">
+      <c r="D162" s="28"/>
+      <c r="E162" s="28"/>
+      <c r="F162" s="29"/>
+      <c r="G162" s="29"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" s="83"/>
+      <c r="B163" s="27">
         <v>232</v>
       </c>
-      <c r="D163" s="29"/>
-      <c r="E163" s="29"/>
-      <c r="F163" s="30"/>
-      <c r="G163" s="30"/>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A164" s="55"/>
-      <c r="B164" s="28">
+      <c r="D163" s="28"/>
+      <c r="E163" s="28"/>
+      <c r="F163" s="29"/>
+      <c r="G163" s="29"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" s="83"/>
+      <c r="B164" s="27">
         <v>233</v>
       </c>
-      <c r="D164" s="29"/>
-      <c r="E164" s="29"/>
-      <c r="F164" s="30"/>
-      <c r="G164" s="30"/>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A165" s="55"/>
-      <c r="B165" s="28">
+      <c r="D164" s="28"/>
+      <c r="E164" s="28"/>
+      <c r="F164" s="29"/>
+      <c r="G164" s="29"/>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" s="83"/>
+      <c r="B165" s="27">
         <v>234</v>
       </c>
-      <c r="C165" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D165" s="29">
+      <c r="C165" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D165" s="28">
         <v>2.13</v>
       </c>
-      <c r="E165" s="29" t="s">
+      <c r="E165" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F165" s="30" t="s">
+      <c r="F165" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G165" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A166" s="55"/>
-      <c r="B166" s="28">
+      <c r="G165" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" s="83"/>
+      <c r="B166" s="27">
         <v>235</v>
       </c>
-      <c r="C166" s="39" t="s">
+      <c r="C166" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="D166" s="29">
+      <c r="D166" s="28">
         <v>1.94</v>
       </c>
-      <c r="E166" s="29"/>
-      <c r="F166" s="30"/>
-      <c r="G166" s="30"/>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A167" s="55"/>
-      <c r="B167" s="28">
+      <c r="E166" s="28"/>
+      <c r="F166" s="29"/>
+      <c r="G166" s="29"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" s="83"/>
+      <c r="B167" s="27">
         <v>236</v>
       </c>
-      <c r="C167" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D167" s="29">
+      <c r="C167" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D167" s="28">
         <v>1.85</v>
       </c>
-      <c r="E167" s="29" t="s">
+      <c r="E167" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F167" s="30" t="s">
+      <c r="F167" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G167" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A168" s="55"/>
-      <c r="B168" s="28">
+      <c r="G167" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" s="83"/>
+      <c r="B168" s="27">
         <v>237</v>
       </c>
-      <c r="D168" s="29"/>
-      <c r="E168" s="29"/>
-      <c r="F168" s="30"/>
-      <c r="G168" s="30"/>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A169" s="55"/>
-      <c r="B169" s="28">
+      <c r="D168" s="28"/>
+      <c r="E168" s="28"/>
+      <c r="F168" s="29"/>
+      <c r="G168" s="29"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" s="83"/>
+      <c r="B169" s="27">
         <v>238</v>
       </c>
-      <c r="D169" s="29"/>
-      <c r="E169" s="29"/>
-      <c r="F169" s="30"/>
-      <c r="G169" s="30"/>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A170" s="55"/>
-      <c r="B170" s="28">
+      <c r="D169" s="28"/>
+      <c r="E169" s="28"/>
+      <c r="F169" s="29"/>
+      <c r="G169" s="29"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" s="83"/>
+      <c r="B170" s="27">
         <v>239</v>
       </c>
-      <c r="D170" s="29"/>
-      <c r="E170" s="29"/>
-      <c r="F170" s="30"/>
-      <c r="G170" s="30"/>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A171" s="55"/>
-      <c r="B171" s="28">
+      <c r="D170" s="28"/>
+      <c r="E170" s="28"/>
+      <c r="F170" s="29"/>
+      <c r="G170" s="29"/>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" s="83"/>
+      <c r="B171" s="27">
         <v>240</v>
       </c>
-      <c r="C171" s="39" t="s">
+      <c r="C171" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="D171" s="29">
+      <c r="D171" s="28">
         <v>1.93</v>
       </c>
-      <c r="E171" s="29"/>
-      <c r="F171" s="30"/>
-      <c r="G171" s="30"/>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A172" s="55"/>
-      <c r="B172" s="28">
+      <c r="E171" s="28"/>
+      <c r="F171" s="29"/>
+      <c r="G171" s="29"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" s="83"/>
+      <c r="B172" s="27">
         <v>241</v>
       </c>
-      <c r="D172" s="29"/>
-      <c r="E172" s="29"/>
-      <c r="F172" s="30"/>
-      <c r="G172" s="30"/>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A173" s="55"/>
-      <c r="B173" s="28">
+      <c r="D172" s="28"/>
+      <c r="E172" s="28"/>
+      <c r="F172" s="29"/>
+      <c r="G172" s="29"/>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" s="83"/>
+      <c r="B173" s="27">
         <v>242</v>
       </c>
-      <c r="D173" s="29"/>
-      <c r="E173" s="29"/>
-      <c r="F173" s="30"/>
-      <c r="G173" s="30"/>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A174" s="55"/>
-      <c r="B174" s="28">
+      <c r="D173" s="28"/>
+      <c r="E173" s="28"/>
+      <c r="F173" s="29"/>
+      <c r="G173" s="29"/>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174" s="83"/>
+      <c r="B174" s="27">
         <v>243</v>
       </c>
-      <c r="C174" s="39" t="s">
+      <c r="C174" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="D174" s="29">
+      <c r="D174" s="28">
         <v>1.93</v>
       </c>
-      <c r="E174" s="29"/>
-      <c r="F174" s="30"/>
-      <c r="G174" s="30"/>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A175" s="55"/>
-      <c r="B175" s="28">
+      <c r="E174" s="28"/>
+      <c r="F174" s="29"/>
+      <c r="G174" s="29"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175" s="83"/>
+      <c r="B175" s="27">
         <v>244</v>
       </c>
-      <c r="D175" s="29"/>
-      <c r="E175" s="29"/>
-      <c r="F175" s="30"/>
-      <c r="G175" s="30"/>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A176" s="55"/>
-      <c r="B176" s="28">
+      <c r="D175" s="28"/>
+      <c r="E175" s="28"/>
+      <c r="F175" s="29"/>
+      <c r="G175" s="29"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A176" s="83"/>
+      <c r="B176" s="27">
         <v>245</v>
       </c>
-      <c r="D176" s="29"/>
-      <c r="E176" s="29"/>
-      <c r="F176" s="30"/>
-      <c r="G176" s="30"/>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A177" s="55"/>
-      <c r="B177" s="28">
+      <c r="D176" s="28"/>
+      <c r="E176" s="28"/>
+      <c r="F176" s="29"/>
+      <c r="G176" s="29"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" s="83"/>
+      <c r="B177" s="27">
         <v>246</v>
       </c>
-      <c r="D177" s="29"/>
-      <c r="E177" s="29"/>
-      <c r="F177" s="30"/>
-      <c r="G177" s="30"/>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A178" s="55"/>
-      <c r="B178" s="28">
+      <c r="D177" s="28"/>
+      <c r="E177" s="28"/>
+      <c r="F177" s="29"/>
+      <c r="G177" s="29"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178" s="83"/>
+      <c r="B178" s="27">
         <v>247</v>
       </c>
-      <c r="C178" s="39" t="s">
+      <c r="C178" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="D178" s="29">
+      <c r="D178" s="28">
         <v>1.93</v>
       </c>
-      <c r="E178" s="29"/>
-      <c r="F178" s="30"/>
-      <c r="G178" s="30"/>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A179" s="55"/>
-      <c r="B179" s="28">
+      <c r="E178" s="28"/>
+      <c r="F178" s="29"/>
+      <c r="G178" s="29"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" s="83"/>
+      <c r="B179" s="27">
         <v>248</v>
       </c>
-      <c r="D179" s="29"/>
-      <c r="E179" s="29"/>
-      <c r="F179" s="30"/>
-      <c r="G179" s="30"/>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A180" s="55"/>
-      <c r="B180" s="28">
+      <c r="D179" s="28"/>
+      <c r="E179" s="28"/>
+      <c r="F179" s="29"/>
+      <c r="G179" s="29"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" s="83"/>
+      <c r="B180" s="27">
         <v>249</v>
       </c>
-      <c r="D180" s="29"/>
-      <c r="E180" s="29"/>
-      <c r="F180" s="30"/>
-      <c r="G180" s="30"/>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A181" s="55"/>
-      <c r="B181" s="28">
+      <c r="D180" s="28"/>
+      <c r="E180" s="28"/>
+      <c r="F180" s="29"/>
+      <c r="G180" s="29"/>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181" s="83"/>
+      <c r="B181" s="27">
         <v>250</v>
       </c>
-      <c r="D181" s="29"/>
-      <c r="E181" s="29"/>
-      <c r="F181" s="30"/>
-      <c r="G181" s="30"/>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A182" s="55"/>
-      <c r="B182" s="28">
+      <c r="D181" s="28"/>
+      <c r="E181" s="28"/>
+      <c r="F181" s="29"/>
+      <c r="G181" s="29"/>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" s="83"/>
+      <c r="B182" s="27">
         <v>251</v>
       </c>
-      <c r="C182" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D182" s="29">
+      <c r="C182" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D182" s="28">
         <v>2.12</v>
       </c>
-      <c r="E182" s="29" t="s">
+      <c r="E182" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F182" s="30" t="s">
+      <c r="F182" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G182" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A183" s="55"/>
-      <c r="B183" s="28">
+      <c r="G182" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A183" s="83"/>
+      <c r="B183" s="27">
         <v>252</v>
       </c>
-      <c r="D183" s="29"/>
-      <c r="E183" s="29"/>
-      <c r="F183" s="30"/>
-      <c r="G183" s="30"/>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A184" s="55"/>
-      <c r="B184" s="28">
+      <c r="D183" s="28"/>
+      <c r="E183" s="28"/>
+      <c r="F183" s="29"/>
+      <c r="G183" s="29"/>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A184" s="83"/>
+      <c r="B184" s="27">
         <v>253</v>
       </c>
-      <c r="D184" s="29"/>
-      <c r="E184" s="29"/>
-      <c r="F184" s="30"/>
-      <c r="G184" s="30"/>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A185" s="55"/>
-      <c r="B185" s="28">
+      <c r="D184" s="28"/>
+      <c r="E184" s="28"/>
+      <c r="F184" s="29"/>
+      <c r="G184" s="29"/>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A185" s="83"/>
+      <c r="B185" s="27">
         <v>254</v>
       </c>
-      <c r="C185" s="39" t="s">
+      <c r="C185" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="D185" s="29">
+      <c r="D185" s="28">
         <v>1.88</v>
       </c>
-      <c r="E185" s="29"/>
-      <c r="F185" s="30"/>
-      <c r="G185" s="30"/>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A186" s="55"/>
-      <c r="B186" s="28">
+      <c r="E185" s="28"/>
+      <c r="F185" s="29"/>
+      <c r="G185" s="29"/>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A186" s="83"/>
+      <c r="B186" s="27">
         <v>255</v>
       </c>
-      <c r="C186" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D186" s="29">
+      <c r="C186" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D186" s="28">
         <v>1.93</v>
       </c>
-      <c r="E186" s="29" t="s">
+      <c r="E186" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F186" s="30" t="s">
+      <c r="F186" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G186" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A187" s="55"/>
-      <c r="B187" s="28">
+      <c r="G186" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A187" s="83"/>
+      <c r="B187" s="27">
         <v>256</v>
       </c>
-      <c r="C187" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D187" s="29">
+      <c r="C187" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D187" s="28">
         <v>1.77</v>
       </c>
-      <c r="E187" s="29" t="s">
+      <c r="E187" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F187" s="30" t="s">
+      <c r="F187" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G187" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A188" s="55"/>
-      <c r="B188" s="28">
+      <c r="G187" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A188" s="83"/>
+      <c r="B188" s="27">
         <v>257</v>
       </c>
-      <c r="C188" s="29" t="s">
+      <c r="C188" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="D188" s="29"/>
-      <c r="E188" s="29"/>
-      <c r="F188" s="30"/>
-      <c r="G188" s="30"/>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A189" s="55"/>
-      <c r="B189" s="28">
+      <c r="D188" s="28"/>
+      <c r="E188" s="28"/>
+      <c r="F188" s="29"/>
+      <c r="G188" s="29"/>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A189" s="83"/>
+      <c r="B189" s="27">
         <v>258</v>
       </c>
-      <c r="D189" s="29"/>
-      <c r="E189" s="29"/>
-      <c r="F189" s="30"/>
-      <c r="G189" s="30"/>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A190" s="55"/>
-      <c r="B190" s="28">
+      <c r="D189" s="28"/>
+      <c r="E189" s="28"/>
+      <c r="F189" s="29"/>
+      <c r="G189" s="29"/>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A190" s="83"/>
+      <c r="B190" s="27">
         <v>259</v>
       </c>
-      <c r="C190" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="D190" s="29">
+      <c r="C190" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D190" s="28">
         <v>2.04</v>
       </c>
-      <c r="E190" s="29" t="s">
+      <c r="E190" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="F190" s="30" t="s">
+      <c r="F190" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="G190" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A191" s="56"/>
-      <c r="B191" s="37">
+      <c r="G190" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A191" s="84"/>
+      <c r="B191" s="36">
         <v>260</v>
       </c>
-      <c r="C191" s="40"/>
-      <c r="D191" s="36"/>
-      <c r="E191" s="36"/>
-      <c r="F191" s="43"/>
-      <c r="G191" s="43"/>
-    </row>
-    <row r="1048576" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1048576" s="39" t="s">
+      <c r="C191" s="39"/>
+      <c r="D191" s="35"/>
+      <c r="E191" s="35"/>
+      <c r="F191" s="42"/>
+      <c r="G191" s="42"/>
+    </row>
+    <row r="1048576" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G1048576" s="38" t="s">
         <v>316</v>
       </c>
     </row>
